--- a/recording_metadata/Cortana_Recording_Metadata.xlsx
+++ b/recording_metadata/Cortana_Recording_Metadata.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="ER" sheetId="1" state="visible" r:id="rId2"/>
@@ -2501,7 +2501,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B35"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.42"/>
   </cols>
@@ -2773,7 +2773,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q57"/>
-  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34.32"/>
@@ -3946,7 +3946,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="0" t="s">
@@ -4015,7 +4015,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H121"/>
-  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="14.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.92"/>
@@ -6555,7 +6555,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="45.11"/>
   </cols>
@@ -6600,7 +6600,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.23"/>
@@ -7127,7 +7127,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.53"/>
@@ -7753,7 +7753,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.86"/>
   </cols>
@@ -7996,7 +7996,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H94"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="9.59"/>
@@ -9709,7 +9709,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C91"/>
-  <sheetFormatPr defaultColWidth="8.9921875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.86"/>
@@ -10701,7 +10701,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F91"/>
-  <sheetFormatPr defaultColWidth="8.9921875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.42"/>
@@ -12319,8 +12319,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
-  <sheetFormatPr defaultColWidth="11.9140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C55"/>
+  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
@@ -12892,6 +12892,30 @@
       </c>
       <c r="C52" s="0" t="s">
         <v>205</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="57" t="n">
+        <v>45278</v>
+      </c>
+      <c r="B53" s="58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="n">
+        <v>45278</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="54" t="n">
+        <v>45278</v>
+      </c>
+      <c r="B55" s="55" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -12911,7 +12935,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I64"/>
-  <sheetFormatPr defaultColWidth="8.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.19"/>
@@ -13583,7 +13607,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E58"/>
-  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.39"/>
@@ -14594,7 +14618,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:S36"/>
-  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.11"/>

--- a/recording_metadata/Cortana_Recording_Metadata.xlsx
+++ b/recording_metadata/Cortana_Recording_Metadata.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ER" sheetId="1" state="visible" r:id="rId2"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="627">
   <si>
     <t xml:space="preserve">Round </t>
   </si>
@@ -1285,6 +1285,9 @@
   </si>
   <si>
     <t xml:space="preserve">1702937566118826_231218_171246_round3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMG</t>
   </si>
   <si>
     <t xml:space="preserve">Original Channels</t>
@@ -2501,7 +2504,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B35"/>
-  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.42"/>
   </cols>
@@ -2773,7 +2776,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q57"/>
-  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34.32"/>
@@ -2788,13 +2791,13 @@
         <v>196</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D1" s="69" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E1" s="69" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F1" s="69" t="s">
         <v>197</v>
@@ -2802,13 +2805,13 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>2.2074101006976</v>
@@ -2822,13 +2825,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>1.91618820713828</v>
@@ -2842,13 +2845,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>2.1549031694575</v>
@@ -2862,13 +2865,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>1.63436939913336</v>
@@ -2882,13 +2885,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>1.50610213394371</v>
@@ -2902,13 +2905,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>2.14014139185557</v>
@@ -2922,13 +2925,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>1.77118649519716</v>
@@ -2942,13 +2945,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>2.72723767707481</v>
@@ -2962,13 +2965,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>1.69976597148251</v>
@@ -2982,13 +2985,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>1.5901745302229</v>
@@ -3002,13 +3005,13 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>4.02906159821023</v>
@@ -3031,13 +3034,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>1.76777113757494</v>
@@ -3051,13 +3054,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>1.63185608974999</v>
@@ -3071,13 +3074,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>1.52138947807465</v>
@@ -3091,13 +3094,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>1.6793716821355</v>
@@ -3111,13 +3114,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>2.54515787946982</v>
@@ -3131,13 +3134,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>4.01472539945866</v>
@@ -3151,13 +3154,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>1.79469654146809</v>
@@ -3171,13 +3174,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>1.44724614904559</v>
@@ -3191,13 +3194,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>2.84117212159127</v>
@@ -3211,13 +3214,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>2.62176931171978</v>
@@ -3231,13 +3234,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>1.60624558373243</v>
@@ -3251,13 +3254,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>2.50231791941221</v>
@@ -3271,13 +3274,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>2.38119735532425</v>
@@ -3291,13 +3294,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>1.99897224402669</v>
@@ -3311,13 +3314,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D27" s="0" t="n">
         <v>1.67433985036413</v>
@@ -3331,13 +3334,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D28" s="0" t="n">
         <v>1.94692117037371</v>
@@ -3351,13 +3354,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D29" s="0" t="n">
         <v>1.48771520027684</v>
@@ -3371,13 +3374,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D30" s="0" t="n">
         <v>1.70880387185988</v>
@@ -3391,13 +3394,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D31" s="0" t="n">
         <v>1.45808984198919</v>
@@ -3411,13 +3414,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D32" s="0" t="n">
         <v>1.48586965365735</v>
@@ -3431,13 +3434,13 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D33" s="0" t="n">
         <v>1.87671517502119</v>
@@ -3451,13 +3454,13 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D34" s="0" t="n">
         <v>1.60512687967736</v>
@@ -3471,13 +3474,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D35" s="0" t="n">
         <v>1.5812425577225</v>
@@ -3491,13 +3494,13 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D36" s="0" t="n">
         <v>2.08130121573154</v>
@@ -3511,13 +3514,13 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D37" s="0" t="n">
         <v>1.58539177480019</v>
@@ -3531,13 +3534,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D38" s="0" t="n">
         <v>2.87319933443605</v>
@@ -3551,13 +3554,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B39" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D39" s="0" t="n">
         <v>2.63965164315008</v>
@@ -3571,13 +3574,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D40" s="0" t="n">
         <v>1.56015382198044</v>
@@ -3591,13 +3594,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D41" s="0" t="n">
         <v>2.34192597660081</v>
@@ -3611,13 +3614,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D42" s="0" t="n">
         <v>1.71588161330883</v>
@@ -3631,13 +3634,13 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B43" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D43" s="0" t="n">
         <v>1.60345746172396</v>
@@ -3651,13 +3654,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D44" s="0" t="n">
         <v>1.77279484716295</v>
@@ -3671,13 +3674,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D45" s="0" t="n">
         <v>1.46904572168543</v>
@@ -3691,13 +3694,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D46" s="0" t="n">
         <v>1.44718215811966</v>
@@ -3711,13 +3714,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" s="0" t="s">
         <v>502</v>
-      </c>
-      <c r="B47" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>501</v>
       </c>
       <c r="D47" s="0" t="n">
         <v>1.5465047856784</v>
@@ -3731,13 +3734,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D48" s="0" t="n">
         <v>1.6694769037473</v>
@@ -3751,13 +3754,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D49" s="0" t="n">
         <v>1.80825978905348</v>
@@ -3771,13 +3774,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D50" s="0" t="n">
         <v>1.50702991416818</v>
@@ -3791,13 +3794,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D51" s="0" t="n">
         <v>1.64248173240046</v>
@@ -3811,13 +3814,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D52" s="0" t="n">
         <v>1.67112657224445</v>
@@ -3831,13 +3834,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D53" s="0" t="n">
         <v>1.52503810145874</v>
@@ -3851,13 +3854,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D54" s="0" t="n">
         <v>1.83132158328407</v>
@@ -3871,13 +3874,13 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D55" s="0" t="n">
         <v>1.70084982084048</v>
@@ -3891,13 +3894,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D56" s="0" t="n">
         <v>1.7452039589713</v>
@@ -3911,13 +3914,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D57" s="0" t="n">
         <v>1.50025155234275</v>
@@ -3946,7 +3949,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="0" t="s">
@@ -3956,12 +3959,12 @@
         <v>205</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>37</v>
@@ -3975,7 +3978,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>26</v>
@@ -3986,7 +3989,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>35</v>
@@ -4015,7 +4018,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H121"/>
-  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="14.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.92"/>
@@ -4033,13 +4036,13 @@
         <v>196</v>
       </c>
       <c r="C1" s="65" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E1" s="65" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F1" s="66" t="s">
         <v>197</v>
@@ -4048,7 +4051,7 @@
         <v>62</v>
       </c>
       <c r="H1" s="66" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4059,7 +4062,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>0</v>
@@ -4079,7 +4082,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="72" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>0</v>
@@ -4099,7 +4102,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="72" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>0</v>
@@ -4119,7 +4122,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="72" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>0</v>
@@ -4139,7 +4142,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="72" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>250</v>
@@ -4159,7 +4162,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="72" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>100</v>
@@ -4179,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>150</v>
@@ -4199,7 +4202,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>400</v>
@@ -4219,7 +4222,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="72" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>200</v>
@@ -4239,7 +4242,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="72" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>0</v>
@@ -4259,7 +4262,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="72" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>0</v>
@@ -4279,7 +4282,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="72" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>200</v>
@@ -4299,7 +4302,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="72" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>150</v>
@@ -4319,7 +4322,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="72" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>150</v>
@@ -4339,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="72" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>100</v>
@@ -4359,7 +4362,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="72" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>400</v>
@@ -4379,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="72" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>100</v>
@@ -4399,7 +4402,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="72" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>100</v>
@@ -4419,7 +4422,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="72" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>100</v>
@@ -4439,7 +4442,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="72" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>0</v>
@@ -4459,7 +4462,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="72" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>0</v>
@@ -4479,7 +4482,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="72" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>0</v>
@@ -4499,7 +4502,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="72" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>0</v>
@@ -4519,7 +4522,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="72" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>0</v>
@@ -4539,7 +4542,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="72" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>0</v>
@@ -4559,7 +4562,7 @@
         <v>3</v>
       </c>
       <c r="C27" s="72" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D27" s="0" t="n">
         <v>0</v>
@@ -4579,7 +4582,7 @@
         <v>3</v>
       </c>
       <c r="C28" s="72" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D28" s="0" t="n">
         <v>0</v>
@@ -4599,7 +4602,7 @@
         <v>3</v>
       </c>
       <c r="C29" s="72" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D29" s="0" t="n">
         <v>700</v>
@@ -4619,7 +4622,7 @@
         <v>4</v>
       </c>
       <c r="C30" s="72" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D30" s="0" t="n">
         <v>0</v>
@@ -4639,7 +4642,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="72" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D31" s="0" t="n">
         <v>0</v>
@@ -4659,7 +4662,7 @@
         <v>4</v>
       </c>
       <c r="C32" s="72" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D32" s="0" t="n">
         <v>0</v>
@@ -4679,7 +4682,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="72" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D33" s="0" t="n">
         <v>0</v>
@@ -4699,7 +4702,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="72" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D34" s="0" t="n">
         <v>250</v>
@@ -4719,7 +4722,7 @@
         <v>4</v>
       </c>
       <c r="C35" s="72" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D35" s="0" t="n">
         <v>250</v>
@@ -4739,7 +4742,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="72" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D36" s="0" t="n">
         <v>0</v>
@@ -4759,7 +4762,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="72" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D37" s="0" t="n">
         <v>0</v>
@@ -4779,7 +4782,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="72" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D38" s="0" t="n">
         <v>0</v>
@@ -4799,7 +4802,7 @@
         <v>3</v>
       </c>
       <c r="C39" s="72" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D39" s="0" t="n">
         <v>0</v>
@@ -4811,7 +4814,7 @@
         <v>198</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4822,7 +4825,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="72" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D40" s="0" t="n">
         <v>0</v>
@@ -4842,7 +4845,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="72" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D41" s="0" t="n">
         <v>200</v>
@@ -4862,7 +4865,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="72" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D42" s="0" t="s">
         <v>64</v>
@@ -4874,7 +4877,7 @@
         <v>198</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4885,7 +4888,7 @@
         <v>2</v>
       </c>
       <c r="C43" s="72" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D43" s="0" t="n">
         <v>200</v>
@@ -4905,7 +4908,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="72" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D44" s="0" t="n">
         <v>250</v>
@@ -4925,7 +4928,7 @@
         <v>3</v>
       </c>
       <c r="C45" s="72" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D45" s="0" t="n">
         <v>0</v>
@@ -4945,7 +4948,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="72" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D46" s="0" t="n">
         <v>250</v>
@@ -4965,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="C47" s="72" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D47" s="0" t="n">
         <v>100</v>
@@ -4985,7 +4988,7 @@
         <v>1</v>
       </c>
       <c r="C48" s="72" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D48" s="0" t="n">
         <v>250</v>
@@ -5005,7 +5008,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D49" s="0" t="n">
         <v>0</v>
@@ -5025,7 +5028,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D50" s="0" t="s">
         <v>64</v>
@@ -5037,7 +5040,7 @@
         <v>198</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5048,7 +5051,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D51" s="0" t="n">
         <v>250</v>
@@ -5068,7 +5071,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D52" s="0" t="n">
         <v>0</v>
@@ -5080,7 +5083,7 @@
         <v>198</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5091,7 +5094,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D53" s="0" t="n">
         <v>0</v>
@@ -5103,7 +5106,7 @@
         <v>198</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5114,7 +5117,7 @@
         <v>2</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D54" s="0" t="n">
         <v>250</v>
@@ -5134,7 +5137,7 @@
         <v>2</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D55" s="0" t="s">
         <v>64</v>
@@ -5146,7 +5149,7 @@
         <v>205</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5157,22 +5160,22 @@
         <v>1</v>
       </c>
       <c r="C56" s="0" t="s">
+        <v>605</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="F56" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="G56" s="0" t="s">
         <v>604</v>
       </c>
-      <c r="D56" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="E56" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="F56" s="0" t="s">
-        <v>198</v>
-      </c>
-      <c r="G56" s="0" t="s">
-        <v>603</v>
-      </c>
       <c r="H56" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5183,7 +5186,7 @@
         <v>1</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D57" s="0" t="s">
         <v>64</v>
@@ -5195,10 +5198,10 @@
         <v>198</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5209,7 +5212,7 @@
         <v>1</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D58" s="0" t="s">
         <v>64</v>
@@ -5221,10 +5224,10 @@
         <v>198</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5235,7 +5238,7 @@
         <v>4</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D59" s="0" t="n">
         <v>0</v>
@@ -5255,7 +5258,7 @@
         <v>4</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D60" s="0" t="n">
         <v>0</v>
@@ -5275,7 +5278,7 @@
         <v>4</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D61" s="0" t="n">
         <v>0</v>
@@ -5295,7 +5298,7 @@
         <v>4</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D62" s="0" t="n">
         <v>250</v>
@@ -5315,7 +5318,7 @@
         <v>4</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D63" s="0" t="n">
         <v>0</v>
@@ -5335,7 +5338,7 @@
         <v>4</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>64</v>
@@ -5347,7 +5350,7 @@
         <v>205</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5358,7 +5361,7 @@
         <v>1</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D65" s="0" t="n">
         <v>0</v>
@@ -5378,7 +5381,7 @@
         <v>1</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D66" s="0" t="n">
         <v>250</v>
@@ -5398,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D67" s="0" t="n">
         <v>100</v>
@@ -5418,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D68" s="0" t="s">
         <v>64</v>
@@ -5430,7 +5433,7 @@
         <v>207</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5441,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D69" s="0" t="n">
         <v>100</v>
@@ -5461,7 +5464,7 @@
         <v>1</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D70" s="0" t="n">
         <v>0</v>
@@ -5481,7 +5484,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>64</v>
@@ -5493,7 +5496,7 @@
         <v>207</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5504,7 +5507,7 @@
         <v>2</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D72" s="0" t="n">
         <v>0</v>
@@ -5524,7 +5527,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D73" s="0" t="n">
         <v>1250</v>
@@ -5544,7 +5547,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D74" s="0" t="n">
         <v>100</v>
@@ -5564,7 +5567,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D75" s="0" t="n">
         <v>0</v>
@@ -5584,7 +5587,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D76" s="0" t="n">
         <v>0</v>
@@ -5604,7 +5607,7 @@
         <v>2</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D77" s="0" t="n">
         <v>250</v>
@@ -5616,7 +5619,7 @@
         <v>207</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5627,7 +5630,7 @@
         <v>1</v>
       </c>
       <c r="C78" s="72" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D78" s="0" t="n">
         <v>100</v>
@@ -5647,7 +5650,7 @@
         <v>1</v>
       </c>
       <c r="C79" s="72" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D79" s="0" t="s">
         <v>64</v>
@@ -5659,7 +5662,7 @@
         <v>207</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5670,7 +5673,7 @@
         <v>2</v>
       </c>
       <c r="C80" s="72" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D80" s="0" t="n">
         <v>0</v>
@@ -5690,7 +5693,7 @@
         <v>2</v>
       </c>
       <c r="C81" s="72" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D81" s="0" t="n">
         <v>250</v>
@@ -5710,7 +5713,7 @@
         <v>2</v>
       </c>
       <c r="C82" s="72" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D82" s="0" t="n">
         <v>0</v>
@@ -5730,7 +5733,7 @@
         <v>2</v>
       </c>
       <c r="C83" s="72" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D83" s="0" t="n">
         <v>250</v>
@@ -5750,7 +5753,7 @@
         <v>2</v>
       </c>
       <c r="C84" s="72" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D84" s="0" t="n">
         <v>200</v>
@@ -5770,7 +5773,7 @@
         <v>2</v>
       </c>
       <c r="C85" s="72" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D85" s="0" t="s">
         <v>64</v>
@@ -5782,7 +5785,7 @@
         <v>207</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5793,7 +5796,7 @@
         <v>3</v>
       </c>
       <c r="C86" s="72" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D86" s="0" t="n">
         <v>0</v>
@@ -5813,7 +5816,7 @@
         <v>3</v>
       </c>
       <c r="C87" s="72" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D87" s="0" t="n">
         <v>250</v>
@@ -5833,7 +5836,7 @@
         <v>3</v>
       </c>
       <c r="C88" s="72" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D88" s="0" t="n">
         <v>1250</v>
@@ -5853,7 +5856,7 @@
         <v>3</v>
       </c>
       <c r="C89" s="72" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D89" s="0" t="n">
         <v>250</v>
@@ -5873,7 +5876,7 @@
         <v>3</v>
       </c>
       <c r="C90" s="72" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D90" s="0" t="n">
         <v>0</v>
@@ -5893,7 +5896,7 @@
         <v>3</v>
       </c>
       <c r="C91" s="72" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D91" s="0" t="n">
         <v>250</v>
@@ -5913,7 +5916,7 @@
         <v>3</v>
       </c>
       <c r="C92" s="72" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D92" s="0" t="n">
         <v>0</v>
@@ -5933,7 +5936,7 @@
         <v>3</v>
       </c>
       <c r="C93" s="72" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D93" s="0" t="n">
         <v>250</v>
@@ -5953,7 +5956,7 @@
         <v>3</v>
       </c>
       <c r="C94" s="72" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D94" s="0" t="n">
         <v>1000</v>
@@ -5973,7 +5976,7 @@
         <v>4</v>
       </c>
       <c r="C95" s="72" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D95" s="0" t="n">
         <v>250</v>
@@ -5993,7 +5996,7 @@
         <v>1</v>
       </c>
       <c r="C96" s="72" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D96" s="0" t="n">
         <v>250</v>
@@ -6013,7 +6016,7 @@
         <v>2</v>
       </c>
       <c r="C97" s="72" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D97" s="0" t="n">
         <v>100</v>
@@ -6033,7 +6036,7 @@
         <v>2</v>
       </c>
       <c r="C98" s="72" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D98" s="0" t="n">
         <v>100</v>
@@ -6053,7 +6056,7 @@
         <v>2</v>
       </c>
       <c r="C99" s="72" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D99" s="0" t="n">
         <v>250</v>
@@ -6065,7 +6068,7 @@
         <v>205</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6076,7 +6079,7 @@
         <v>2</v>
       </c>
       <c r="C100" s="72" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D100" s="0" t="n">
         <v>250</v>
@@ -6096,7 +6099,7 @@
         <v>2</v>
       </c>
       <c r="C101" s="72" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D101" s="0" t="n">
         <v>200</v>
@@ -6108,7 +6111,7 @@
         <v>205</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6119,7 +6122,7 @@
         <v>3</v>
       </c>
       <c r="C102" s="72" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D102" s="0" t="n">
         <v>250</v>
@@ -6139,7 +6142,7 @@
         <v>2</v>
       </c>
       <c r="C103" s="72" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D103" s="0" t="n">
         <v>100</v>
@@ -6159,7 +6162,7 @@
         <v>2</v>
       </c>
       <c r="C104" s="72" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D104" s="0" t="n">
         <v>200</v>
@@ -6179,7 +6182,7 @@
         <v>2</v>
       </c>
       <c r="C105" s="72" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D105" s="0" t="n">
         <v>200</v>
@@ -6199,7 +6202,7 @@
         <v>3</v>
       </c>
       <c r="C106" s="72" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D106" s="0" t="n">
         <v>300</v>
@@ -6219,7 +6222,7 @@
         <v>1</v>
       </c>
       <c r="C107" s="72" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D107" s="0" t="s">
         <v>64</v>
@@ -6231,7 +6234,7 @@
         <v>207</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6242,7 +6245,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="72" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D108" s="0" t="n">
         <v>0</v>
@@ -6262,7 +6265,7 @@
         <v>1</v>
       </c>
       <c r="C109" s="72" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D109" s="0" t="n">
         <v>100</v>
@@ -6282,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="C110" s="72" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D110" s="0" t="n">
         <v>100</v>
@@ -6294,7 +6297,7 @@
         <v>207</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6305,7 +6308,7 @@
         <v>2</v>
       </c>
       <c r="C111" s="72" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D111" s="0" t="n">
         <v>0</v>
@@ -6325,7 +6328,7 @@
         <v>2</v>
       </c>
       <c r="C112" s="72" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D112" s="0" t="n">
         <v>0</v>
@@ -6337,7 +6340,7 @@
         <v>207</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6348,7 +6351,7 @@
         <v>2</v>
       </c>
       <c r="C113" s="72" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D113" s="0" t="n">
         <v>0</v>
@@ -6368,7 +6371,7 @@
         <v>2</v>
       </c>
       <c r="C114" s="72" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D114" s="0" t="n">
         <v>0</v>
@@ -6388,7 +6391,7 @@
         <v>2</v>
       </c>
       <c r="C115" s="72" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D115" s="0" t="s">
         <v>64</v>
@@ -6400,7 +6403,7 @@
         <v>207</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6411,7 +6414,7 @@
         <v>2</v>
       </c>
       <c r="C116" s="72" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D116" s="0" t="n">
         <v>0</v>
@@ -6431,7 +6434,7 @@
         <v>2</v>
       </c>
       <c r="C117" s="72" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D117" s="0" t="n">
         <v>0</v>
@@ -6443,7 +6446,7 @@
         <v>207</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6454,7 +6457,7 @@
         <v>2</v>
       </c>
       <c r="C118" s="72" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D118" s="0" t="n">
         <v>1000</v>
@@ -6466,7 +6469,7 @@
         <v>207</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6477,7 +6480,7 @@
         <v>1</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D119" s="0" t="s">
         <v>64</v>
@@ -6489,7 +6492,7 @@
         <v>207</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6500,7 +6503,7 @@
         <v>2</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D120" s="0" t="s">
         <v>64</v>
@@ -6512,7 +6515,7 @@
         <v>207</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6523,7 +6526,7 @@
         <v>2</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D121" s="0" t="s">
         <v>64</v>
@@ -6535,7 +6538,7 @@
         <v>207</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -6555,7 +6558,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="45.11"/>
   </cols>
@@ -6568,7 +6571,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="72" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D1" s="0" t="n">
         <v>250</v>
@@ -6580,7 +6583,7 @@
         <v>198</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -6600,7 +6603,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.23"/>
@@ -6615,13 +6618,13 @@
         <v>196</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F1" s="0" t="s">
         <v>197</v>
@@ -6635,10 +6638,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E2" s="0" t="n">
         <v>0.030965715390678</v>
@@ -6655,10 +6658,10 @@
         <v>3</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>0.0001048561426</v>
@@ -6675,10 +6678,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>0.03527854547184</v>
@@ -6695,10 +6698,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>0.000378311542831</v>
@@ -6715,10 +6718,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>1.05830081034659E-006</v>
@@ -6735,10 +6738,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>2.13976612550698E-005</v>
@@ -6755,10 +6758,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>7.55699317281293E-011</v>
@@ -6775,10 +6778,10 @@
         <v>2</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>1.66280772505988E-005</v>
@@ -6795,10 +6798,10 @@
         <v>3</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E10" s="0" t="n">
         <v>2.33114874428906E-005</v>
@@ -6815,10 +6818,10 @@
         <v>3</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E11" s="0" t="n">
         <v>0.012545428798116</v>
@@ -6835,10 +6838,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E12" s="0" t="n">
         <v>0.038781460115805</v>
@@ -6855,10 +6858,10 @@
         <v>3</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>0.042377881281726</v>
@@ -6875,10 +6878,10 @@
         <v>4</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E14" s="0" t="n">
         <v>0.011944886356068</v>
@@ -6895,10 +6898,10 @@
         <v>4</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E15" s="0" t="n">
         <v>0.00029232953002</v>
@@ -6915,10 +6918,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E16" s="0" t="n">
         <v>0.00986766757997</v>
@@ -6935,10 +6938,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E17" s="0" t="n">
         <v>1.49682454822413E-005</v>
@@ -6955,10 +6958,10 @@
         <v>3</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E18" s="0" t="n">
         <v>0.009555414268796</v>
@@ -6975,10 +6978,10 @@
         <v>3</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E19" s="0" t="n">
         <v>0.001540377255957</v>
@@ -6995,10 +6998,10 @@
         <v>2</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E20" s="0" t="n">
         <v>0.01126620279013</v>
@@ -7015,10 +7018,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E21" s="0" t="n">
         <v>0.006289624603342</v>
@@ -7035,10 +7038,10 @@
         <v>4</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E22" s="0" t="n">
         <v>0.006514719781525</v>
@@ -7055,10 +7058,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E23" s="0" t="n">
         <v>0.004480491399968</v>
@@ -7075,10 +7078,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E24" s="0" t="n">
         <v>0.011429781534636</v>
@@ -7095,10 +7098,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E25" s="0" t="n">
         <v>0.000335148307695</v>
@@ -7127,7 +7130,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.53"/>
@@ -7143,13 +7146,13 @@
         <v>196</v>
       </c>
       <c r="C1" s="65" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E1" s="65" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7160,7 +7163,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>0</v>
@@ -7177,7 +7180,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="72" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>0</v>
@@ -7194,7 +7197,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>100</v>
@@ -7211,7 +7214,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>0</v>
@@ -7228,7 +7231,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>500</v>
@@ -7245,7 +7248,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>0</v>
@@ -7262,7 +7265,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>0</v>
@@ -7279,7 +7282,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>0</v>
@@ -7296,7 +7299,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>250</v>
@@ -7313,7 +7316,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>0</v>
@@ -7330,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>0</v>
@@ -7347,7 +7350,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>250</v>
@@ -7364,7 +7367,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>0</v>
@@ -7381,7 +7384,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>0</v>
@@ -7398,7 +7401,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>0</v>
@@ -7415,7 +7418,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>250</v>
@@ -7432,7 +7435,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>0</v>
@@ -7449,7 +7452,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>250</v>
@@ -7466,7 +7469,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>0</v>
@@ -7483,7 +7486,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>0</v>
@@ -7500,7 +7503,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>0</v>
@@ -7517,7 +7520,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>0</v>
@@ -7534,7 +7537,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>250</v>
@@ -7551,7 +7554,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>0</v>
@@ -7568,7 +7571,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>0</v>
@@ -7585,7 +7588,7 @@
         <v>3</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D27" s="0" t="n">
         <v>0</v>
@@ -7602,7 +7605,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D28" s="0" t="n">
         <v>0</v>
@@ -7619,7 +7622,7 @@
         <v>3</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D29" s="0" t="n">
         <v>0</v>
@@ -7636,7 +7639,7 @@
         <v>3</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D30" s="0" t="n">
         <v>250</v>
@@ -7653,7 +7656,7 @@
         <v>3</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D31" s="0" t="n">
         <v>250</v>
@@ -7670,7 +7673,7 @@
         <v>1</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D32" s="0" t="n">
         <v>0</v>
@@ -7687,7 +7690,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D33" s="0" t="n">
         <v>0</v>
@@ -7704,7 +7707,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D34" s="0" t="n">
         <v>250</v>
@@ -7721,7 +7724,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D35" s="0" t="n">
         <v>0</v>
@@ -7753,7 +7756,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.86"/>
   </cols>
@@ -7996,7 +7999,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H94"/>
-  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="9.59"/>
@@ -9709,7 +9712,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C91"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.86"/>
@@ -10701,7 +10704,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F91"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.42"/>
@@ -12320,7 +12323,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C55"/>
-  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.94140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
@@ -12341,7 +12344,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12352,7 +12355,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12363,7 +12366,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12374,7 +12377,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12385,7 +12388,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12396,7 +12399,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12407,7 +12410,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12418,7 +12421,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12429,7 +12432,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12440,7 +12443,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12451,7 +12454,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12462,7 +12465,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12473,7 +12476,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12484,7 +12487,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12495,7 +12498,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12506,7 +12509,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12517,7 +12520,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12528,7 +12531,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12539,7 +12542,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12550,7 +12553,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12561,7 +12564,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12572,7 +12575,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12583,7 +12586,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>198</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12901,6 +12904,9 @@
       <c r="B53" s="58" t="n">
         <v>1</v>
       </c>
+      <c r="C53" s="0" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="n">
@@ -12909,6 +12915,9 @@
       <c r="B54" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="C54" s="0" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="54" t="n">
@@ -12916,6 +12925,9 @@
       </c>
       <c r="B55" s="55" t="n">
         <v>3</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -12935,7 +12947,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I64"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.19"/>
@@ -12954,22 +12966,22 @@
         <v>58</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12983,13 +12995,13 @@
         <v>214</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13003,10 +13015,10 @@
         <v>216</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13020,11 +13032,11 @@
         <v>218</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E4" s="56"/>
       <c r="F4" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13041,7 +13053,7 @@
         <v>64</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13092,7 +13104,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13106,10 +13118,10 @@
         <v>230</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>45032</v>
@@ -13126,13 +13138,13 @@
         <v>232</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>45032</v>
@@ -13152,13 +13164,13 @@
         <v>234</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>45031</v>
@@ -13212,10 +13224,10 @@
         <v>240</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13229,10 +13241,10 @@
         <v>241</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13246,10 +13258,10 @@
         <v>243</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13263,10 +13275,10 @@
         <v>245</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13280,10 +13292,10 @@
         <v>247</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13297,10 +13309,10 @@
         <v>249</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13314,10 +13326,10 @@
         <v>251</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13520,7 +13532,7 @@
         <v>45383</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13532,7 +13544,7 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5" t="n">
@@ -13542,7 +13554,7 @@
         <v>45383</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13554,7 +13566,7 @@
       </c>
       <c r="C56" s="64"/>
       <c r="D56" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G56" s="5" t="n">
         <v>45383</v>
@@ -13563,7 +13575,7 @@
         <v>45383</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13607,7 +13619,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E58"/>
-  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.39"/>
@@ -13623,10 +13635,10 @@
         <v>196</v>
       </c>
       <c r="C1" s="65" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1" s="66" t="s">
         <v>197</v>
@@ -13634,13 +13646,13 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>0.000167347651247531</v>
@@ -13651,13 +13663,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>0.00183374075083306</v>
@@ -13668,13 +13680,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>0.000272504256866232</v>
@@ -13685,13 +13697,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>0.0292681461802767</v>
@@ -13702,13 +13714,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>0.0408544513448368</v>
@@ -13719,13 +13731,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>0.0157046582446898</v>
@@ -13736,13 +13748,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>0.0370030470217893</v>
@@ -13753,13 +13765,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>0.00030485139103684</v>
@@ -13770,13 +13782,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>1.5753190717376E-006</v>
@@ -13787,13 +13799,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>0.00551306886663384</v>
@@ -13804,13 +13816,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>0.0203493517653912</v>
@@ -13821,13 +13833,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="67" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B13" s="67" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D13" s="67" t="n">
         <v>0.0093569117500219</v>
@@ -13838,13 +13850,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>7.16834396218083E-012</v>
@@ -13855,13 +13867,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>0.00567551921407011</v>
@@ -13872,13 +13884,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>0.0324084567043176</v>
@@ -13889,13 +13901,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>0.0152606785752719</v>
@@ -13906,13 +13918,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>0.0108783273244698</v>
@@ -13923,13 +13935,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="67" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B19" s="67" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="67" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D19" s="67" t="n">
         <v>6.6312123780865E-012</v>
@@ -13940,13 +13952,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>7.80299610061578E-006</v>
@@ -13957,13 +13969,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>0.0179897142885999</v>
@@ -13974,13 +13986,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>0.00452884431580007</v>
@@ -13991,13 +14003,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>3.87812384813526E-006</v>
@@ -14008,13 +14020,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>1.15036720241586E-005</v>
@@ -14025,13 +14037,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>5.0802631434574E-007</v>
@@ -14042,13 +14054,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>3.48005489557259E-005</v>
@@ -14059,13 +14071,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D27" s="0" t="n">
         <v>0.000909303064193552</v>
@@ -14076,13 +14088,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D28" s="0" t="n">
         <v>0.00137042128127269</v>
@@ -14093,13 +14105,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D29" s="0" t="n">
         <v>0.0402955062172857</v>
@@ -14110,13 +14122,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D30" s="0" t="n">
         <v>0.0110877305932871</v>
@@ -14127,13 +14139,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D31" s="0" t="n">
         <v>0.0399456110435245</v>
@@ -14144,13 +14156,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D32" s="0" t="n">
         <v>0.00862296916201926</v>
@@ -14161,13 +14173,13 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="67" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B33" s="67" t="n">
         <v>3</v>
       </c>
       <c r="C33" s="67" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D33" s="67" t="n">
         <v>0.0482858559404872</v>
@@ -14178,13 +14190,13 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="67" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B34" s="67" t="n">
         <v>2</v>
       </c>
       <c r="C34" s="67" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D34" s="67" t="n">
         <v>0.00239737276432677</v>
@@ -14195,13 +14207,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D35" s="0" t="n">
         <v>0.0404251274716832</v>
@@ -14212,13 +14224,13 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D36" s="0" t="n">
         <v>0.0213915212994397</v>
@@ -14229,13 +14241,13 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D37" s="0" t="n">
         <v>0.0181306288529609</v>
@@ -14246,13 +14258,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D38" s="0" t="n">
         <v>0.000371456787101544</v>
@@ -14263,13 +14275,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="67" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B39" s="67" t="n">
         <v>4</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D39" s="67" t="n">
         <v>0.0259924251683769</v>
@@ -14280,13 +14292,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D40" s="0" t="n">
         <v>0.021951365810948</v>
@@ -14297,13 +14309,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D41" s="0" t="n">
         <v>5.52169283538707E-007</v>
@@ -14314,13 +14326,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D42" s="0" t="n">
         <v>4.46843053651836E-006</v>
@@ -14331,13 +14343,13 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B43" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D43" s="0" t="n">
         <v>5.99143685263841E-005</v>
@@ -14348,13 +14360,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D44" s="0" t="n">
         <v>0.00818486262907165</v>
@@ -14365,13 +14377,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D45" s="0" t="n">
         <v>0.00534908622982942</v>
@@ -14382,13 +14394,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D46" s="0" t="n">
         <v>0.0183427990773176</v>
@@ -14399,13 +14411,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B47" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D47" s="0" t="n">
         <v>0.0450375913084286</v>
@@ -14416,13 +14428,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D48" s="0" t="n">
         <v>0.0137207438451637</v>
@@ -14433,13 +14445,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" s="0" t="s">
         <v>502</v>
-      </c>
-      <c r="B49" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>501</v>
       </c>
       <c r="D49" s="0" t="n">
         <v>0.0308159014622524</v>
@@ -14450,13 +14462,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D50" s="0" t="n">
         <v>0.0139354605217081</v>
@@ -14467,13 +14479,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D51" s="0" t="n">
         <v>0.00408222428481898</v>
@@ -14484,13 +14496,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D52" s="0" t="n">
         <v>0.0352229638559858</v>
@@ -14501,13 +14513,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D53" s="0" t="n">
         <v>0.0113482599171506</v>
@@ -14518,13 +14530,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D54" s="0" t="n">
         <v>0.0312767076889777</v>
@@ -14535,13 +14547,13 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D55" s="0" t="n">
         <v>0.00517590455590829</v>
@@ -14552,13 +14564,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D56" s="0" t="n">
         <v>0.00914148375940307</v>
@@ -14569,13 +14581,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D57" s="0" t="n">
         <v>0.0368202416860903</v>
@@ -14586,13 +14598,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B58" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D58" s="0" t="n">
         <v>0.00658281460550913</v>
@@ -14618,7 +14630,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:S36"/>
-  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.11"/>
@@ -14644,22 +14656,22 @@
         <v>196</v>
       </c>
       <c r="C1" s="65" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E1" s="65" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F1" s="65" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G1" s="65" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1" s="65" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I1" s="66" t="s">
         <v>197</v>
@@ -14675,19 +14687,19 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>0.787376130022259</v>
@@ -14696,7 +14708,7 @@
         <v>0.00141302462633323</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I2" s="0" t="s">
         <v>198</v>
@@ -14704,19 +14716,19 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>0.714149977396184</v>
@@ -14725,7 +14737,7 @@
         <v>0.00412742172835764</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I3" s="0" t="s">
         <v>198</v>
@@ -14733,19 +14745,19 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>0.72507271030454</v>
@@ -14754,7 +14766,7 @@
         <v>0.00358126617515756</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I4" s="0" t="s">
         <v>198</v>
@@ -14762,19 +14774,19 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>0.734398082547392</v>
@@ -14783,7 +14795,7 @@
         <v>0.00315892887014564</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I5" s="0" t="s">
         <v>198</v>
@@ -14791,19 +14803,19 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>0.737640600753071</v>
@@ -14812,7 +14824,7 @@
         <v>0.00302108700727468</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I6" s="0" t="s">
         <v>198</v>
@@ -14820,19 +14832,19 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>0.715588361621035</v>
@@ -14841,7 +14853,7 @@
         <v>0.00405219461072609</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I7" s="0" t="s">
         <v>198</v>
@@ -14849,19 +14861,19 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>0.784349723093875</v>
@@ -14870,7 +14882,7 @@
         <v>0.00148681503277446</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I8" s="0" t="s">
         <v>198</v>
@@ -14878,19 +14890,19 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F9" s="0" t="n">
         <v>0.730766294167097</v>
@@ -14899,7 +14911,7 @@
         <v>0.00331876839660095</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>198</v>
@@ -14907,19 +14919,19 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F10" s="0" t="n">
         <v>0.846114075952503</v>
@@ -14928,7 +14940,7 @@
         <v>0.000443570824989244</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I10" s="0" t="s">
         <v>198</v>
@@ -14936,19 +14948,19 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F11" s="0" t="n">
         <v>0.707474625239755</v>
@@ -14957,7 +14969,7 @@
         <v>0.00449016011444848</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I11" s="0" t="s">
         <v>198</v>
@@ -14965,19 +14977,19 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F12" s="0" t="n">
         <v>0.785878208761381</v>
@@ -14986,7 +14998,7 @@
         <v>0.00144920361429895</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I12" s="0" t="s">
         <v>198</v>
@@ -14994,19 +15006,19 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F13" s="0" t="n">
         <v>0.780344297275339</v>
@@ -15015,7 +15027,7 @@
         <v>0.00158876527841905</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I13" s="0" t="s">
         <v>198</v>
@@ -15023,19 +15035,19 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F14" s="0" t="n">
         <v>0.707129353187573</v>
@@ -15044,7 +15056,7 @@
         <v>0.00450954256313961</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I14" s="0" t="s">
         <v>198</v>
@@ -15052,19 +15064,19 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F15" s="0" t="n">
         <v>0.803988782853755</v>
@@ -15073,7 +15085,7 @@
         <v>0.00105462762655855</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I15" s="0" t="s">
         <v>198</v>
@@ -15081,19 +15093,19 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F16" s="0" t="n">
         <v>0.763699249257595</v>
@@ -15102,7 +15114,7 @@
         <v>0.00206810438085801</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I16" s="0" t="s">
         <v>198</v>
@@ -15110,19 +15122,19 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="67" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B17" s="67" t="n">
         <v>3</v>
       </c>
       <c r="C17" s="67" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D17" s="67" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E17" s="67" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F17" s="67" t="n">
         <v>0.881204837525589</v>
@@ -15131,7 +15143,7 @@
         <v>0.000176549182897429</v>
       </c>
       <c r="H17" s="67" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I17" s="67" t="s">
         <v>198</v>
@@ -15139,19 +15151,19 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F18" s="0" t="n">
         <v>0.707101280411521</v>
@@ -15160,7 +15172,7 @@
         <v>0.00451112119911595</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I18" s="0" t="s">
         <v>198</v>
@@ -15168,19 +15180,19 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F19" s="0" t="n">
         <v>0.751328262794826</v>
@@ -15189,7 +15201,7 @@
         <v>0.00248752021453756</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I19" s="0" t="s">
         <v>198</v>
@@ -15197,19 +15209,19 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F20" s="0" t="n">
         <v>0.749550371405668</v>
@@ -15218,7 +15230,7 @@
         <v>0.00255256196778632</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I20" s="0" t="s">
         <v>198</v>
@@ -15226,19 +15238,19 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="67" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B21" s="67" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="67" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D21" s="67" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E21" s="67" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F21" s="67" t="n">
         <v>0.720424149392981</v>
@@ -15247,7 +15259,7 @@
         <v>0.0038067080589425</v>
       </c>
       <c r="H21" s="67" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I21" s="67" t="s">
         <v>198</v>
@@ -15255,19 +15267,19 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F22" s="0" t="n">
         <v>0.707149139381861</v>
@@ -15276,7 +15288,7 @@
         <v>0.00450843015836554</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="I22" s="0" t="s">
         <v>198</v>
@@ -15284,19 +15296,19 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F23" s="0" t="n">
         <v>0.832865788003454</v>
@@ -15305,7 +15317,7 @@
         <v>0.000595776942024419</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>198</v>
@@ -15313,19 +15325,19 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F24" s="0" t="n">
         <v>0.74158029584605</v>
@@ -15334,7 +15346,7 @@
         <v>0.0028596364130994</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>198</v>
@@ -15342,19 +15354,19 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="67" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B25" s="67" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="67" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D25" s="67" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E25" s="67" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F25" s="67" t="n">
         <v>0.735073400638693</v>
@@ -15363,7 +15375,7 @@
         <v>0.00312984579624553</v>
       </c>
       <c r="H25" s="67" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I25" s="67" t="s">
         <v>198</v>
@@ -15371,19 +15383,19 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B26" s="67" t="n">
         <v>2</v>
       </c>
       <c r="C26" s="67" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D26" s="67" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E26" s="67" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F26" s="67" t="n">
         <v>0.711185571486803</v>
@@ -15392,7 +15404,7 @@
         <v>0.00428571572931137</v>
       </c>
       <c r="H26" s="67" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I26" s="67" t="s">
         <v>198</v>
@@ -15400,19 +15412,19 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F27" s="0" t="n">
         <v>0.72106861365433</v>
@@ -15421,7 +15433,7 @@
         <v>0.00377484369911458</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I27" s="0" t="s">
         <v>198</v>
@@ -15429,19 +15441,19 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="67" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B28" s="67" t="n">
         <v>4</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D28" s="67" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E28" s="67" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F28" s="67" t="n">
         <v>0.737807282466348</v>
@@ -15450,7 +15462,7 @@
         <v>0.0030141233437616</v>
       </c>
       <c r="H28" s="67" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="I28" s="67" t="s">
         <v>205</v>
@@ -15458,19 +15470,19 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F29" s="0" t="n">
         <v>0.733031250915402</v>
@@ -15479,7 +15491,7 @@
         <v>0.00321840215280912</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="I29" s="0" t="s">
         <v>205</v>
@@ -15487,19 +15499,19 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F30" s="0" t="n">
         <v>0.723125387871428</v>
@@ -15508,7 +15520,7 @@
         <v>0.00367446840750216</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I30" s="0" t="s">
         <v>205</v>
@@ -15516,19 +15528,19 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F31" s="0" t="n">
         <v>0.713139104979482</v>
@@ -15537,7 +15549,7 @@
         <v>0.0041809052804653</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="I31" s="0" t="s">
         <v>205</v>
@@ -15545,19 +15557,19 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F32" s="0" t="n">
         <v>0.807758238850952</v>
@@ -15566,7 +15578,7 @@
         <v>0.000983606536464546</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I32" s="0" t="s">
         <v>205</v>
@@ -15574,19 +15586,19 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F33" s="0" t="n">
         <v>0.769683282494715</v>
@@ -15595,7 +15607,7 @@
         <v>0.0018850560139879</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="I33" s="0" t="s">
         <v>205</v>
@@ -15603,19 +15615,19 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F34" s="0" t="n">
         <v>0.727748137795628</v>
@@ -15624,7 +15636,7 @@
         <v>0.00345607911942881</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="I34" s="0" t="s">
         <v>205</v>
@@ -15632,19 +15644,19 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F35" s="0" t="n">
         <v>0.741751688201506</v>
@@ -15653,7 +15665,7 @@
         <v>0.00285276032610502</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="I35" s="0" t="s">
         <v>205</v>
@@ -15661,19 +15673,19 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F36" s="0" t="n">
         <v>0.807996431921935</v>
@@ -15682,7 +15694,7 @@
         <v>0.000979239335847504</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I36" s="0" t="s">
         <v>205</v>

--- a/recording_metadata/Cortana_Recording_Metadata.xlsx
+++ b/recording_metadata/Cortana_Recording_Metadata.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="ER" sheetId="1" state="visible" r:id="rId2"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="667">
   <si>
     <t xml:space="preserve">Round </t>
   </si>
@@ -1032,84 +1032,126 @@
     <t xml:space="preserve">1699728895878795_231111_135457_round1</t>
   </si>
   <si>
+    <t xml:space="preserve">231111_round1</t>
+  </si>
+  <si>
     <t xml:space="preserve">15, 30, 16, 8, 2, 29, 7, 13, 24, 3, 4, 27, 22, 26, 5, 11, 6, 18, 10, 2, 14</t>
   </si>
   <si>
     <t xml:space="preserve">1699732280034649_231111_145120_round2</t>
   </si>
   <si>
+    <t xml:space="preserve">231111_round2</t>
+  </si>
+  <si>
     <t xml:space="preserve">0, 31, 13, 3, 26, 5, 21, 7, 28, 19, 9</t>
   </si>
   <si>
     <t xml:space="preserve">1699818518132744_231112_144838_round1</t>
   </si>
   <si>
+    <t xml:space="preserve">231112_round1</t>
+  </si>
+  <si>
     <t xml:space="preserve">13, 9, 22, 20, 21, 6, 0, 31, 4, 12, 19</t>
   </si>
   <si>
     <t xml:space="preserve">1699820709714145_231112_152510_round2</t>
   </si>
   <si>
+    <t xml:space="preserve">231112_round2</t>
+  </si>
+  <si>
     <t xml:space="preserve">28, 18, 7, 2, 5, 26, 13</t>
   </si>
   <si>
     <t xml:space="preserve">1700246799607370_231117_134641_round1</t>
   </si>
   <si>
+    <t xml:space="preserve">231117_round1</t>
+  </si>
+  <si>
     <t xml:space="preserve">0, 31, 14, 17, 12, 8, 2</t>
   </si>
   <si>
     <t xml:space="preserve">1700249668699210_231117_143429_round2</t>
   </si>
   <si>
+    <t xml:space="preserve">231117_round2</t>
+  </si>
+  <si>
     <t xml:space="preserve">0, 31, 14, 29, 17, 15, 13, 20, 5, 6</t>
   </si>
   <si>
     <t xml:space="preserve">1700515129849329_231120_161851_round1</t>
   </si>
   <si>
+    <t xml:space="preserve">231120_round1</t>
+  </si>
+  <si>
     <t xml:space="preserve">9, 28, 18, 7, 29, 10, 6 </t>
   </si>
   <si>
     <t xml:space="preserve">1700518870846120_231120_172111_round2</t>
   </si>
   <si>
+    <t xml:space="preserve">231120_round2</t>
+  </si>
+  <si>
     <t xml:space="preserve">18, 19, 4, 27, 9, 22, 26, 11, 20, 10, 21</t>
   </si>
   <si>
     <t xml:space="preserve">1700677704435485_231122_132825_round1</t>
   </si>
   <si>
+    <t xml:space="preserve">231122_round1</t>
+  </si>
+  <si>
     <t xml:space="preserve">3, 28, 12, 27, 9, 22, 11, 20, 6, 9, 4</t>
   </si>
   <si>
     <t xml:space="preserve">1700680238840672_231122_141039_round2</t>
   </si>
   <si>
+    <t xml:space="preserve">231122_round2</t>
+  </si>
+  <si>
     <t xml:space="preserve">24, 3, 28, 4, 22, 27, 11, 20, 6</t>
   </si>
   <si>
     <t xml:space="preserve">1700683397101186_231122_150317_round3</t>
   </si>
   <si>
+    <t xml:space="preserve">231122_round3</t>
+  </si>
+  <si>
     <t xml:space="preserve">14, 17, 2, 29, 18, 7, 3, 12, 24, 22, 11, 20</t>
   </si>
   <si>
     <t xml:space="preserve">1700685906147543_231122_154506_round4</t>
   </si>
   <si>
+    <t xml:space="preserve">231122_round4</t>
+  </si>
+  <si>
     <t xml:space="preserve">29, 14, 17, 13, 3, 12, 24, 28, 19, 4, 27, 9, 22</t>
   </si>
   <si>
     <t xml:space="preserve">1700928025837081_231125_110027_round1</t>
   </si>
   <si>
+    <t xml:space="preserve">231125_round1</t>
+  </si>
+  <si>
     <t xml:space="preserve">16, 1, 0, 17, 2, 29, 13, 18, 7, 24, 3</t>
   </si>
   <si>
     <t xml:space="preserve">1700930905266498_231125_114825_round2</t>
   </si>
   <si>
+    <t xml:space="preserve">231125_round2</t>
+  </si>
+  <si>
     <t xml:space="preserve">14, 17, 2, 29, 13, 18, 7, 24, 22, 11</t>
   </si>
   <si>
@@ -1125,18 +1167,27 @@
     <t xml:space="preserve">1701112046359920_231127_140727_round1</t>
   </si>
   <si>
+    <t xml:space="preserve">231127_round1</t>
+  </si>
+  <si>
     <t xml:space="preserve">14, 7, 24, 3, 28, 22, 12, 11, 20</t>
   </si>
   <si>
     <t xml:space="preserve">1701114400931648_231127_144641_round2</t>
   </si>
   <si>
+    <t xml:space="preserve">231127_round2</t>
+  </si>
+  <si>
     <t xml:space="preserve">2, 14, 17, 28, 29, 18, 31, 24, 3, 7</t>
   </si>
   <si>
     <t xml:space="preserve">1701117230798947_231127_153351_round3</t>
   </si>
   <si>
+    <t xml:space="preserve">231127_round3</t>
+  </si>
+  <si>
     <t xml:space="preserve">8, 23, 30, 0, 14, 17, 2</t>
   </si>
   <si>
@@ -1146,6 +1197,9 @@
     <t xml:space="preserve">1701199373465155_231128_142255_round1</t>
   </si>
   <si>
+    <t xml:space="preserve">231128_round1</t>
+  </si>
+  <si>
     <t xml:space="preserve">15, 16, 31, 14, 24</t>
   </si>
   <si>
@@ -1155,78 +1209,117 @@
     <t xml:space="preserve">1701201672630153_231128_150113_round2</t>
   </si>
   <si>
+    <t xml:space="preserve">231128_round2</t>
+  </si>
+  <si>
     <t xml:space="preserve">15, 16, 1, 7, 24, 28, 12, 19, 4, 27, 9</t>
   </si>
   <si>
     <t xml:space="preserve">1701204290206039_231128_154450_round3</t>
   </si>
   <si>
+    <t xml:space="preserve">231128_round3</t>
+  </si>
+  <si>
     <t xml:space="preserve">15, 16, 7, 24, 3, 28, 12, 4, 27</t>
   </si>
   <si>
     <t xml:space="preserve">1701206578266559_231128_162258_round4</t>
   </si>
   <si>
+    <t xml:space="preserve">231128_round4</t>
+  </si>
+  <si>
     <t xml:space="preserve">11, 7, 2, 25, 15, 16, 0</t>
   </si>
   <si>
     <t xml:space="preserve">1701800906523706_231205_132827_round1</t>
   </si>
   <si>
+    <t xml:space="preserve">231205_round1</t>
+  </si>
+  <si>
     <t xml:space="preserve">4, 22, 26, 10, 21, 6, 25</t>
   </si>
   <si>
     <t xml:space="preserve">1701803100561980_231205_140501_round2</t>
   </si>
   <si>
+    <t xml:space="preserve">231205_round2</t>
+  </si>
+  <si>
     <t xml:space="preserve">22, 11, 9, 5, 26, 10, 21, 25</t>
   </si>
   <si>
     <t xml:space="preserve">1701805390576805_231205_144311_round3</t>
   </si>
   <si>
+    <t xml:space="preserve">231205_round3</t>
+  </si>
+  <si>
     <t xml:space="preserve">15, 16, 8, 31, 3, 14, 12, 27, 26, 10, 11, 25</t>
   </si>
   <si>
     <t xml:space="preserve">1701808679484182_231205_153800_round4</t>
   </si>
   <si>
+    <t xml:space="preserve">231205_round4</t>
+  </si>
+  <si>
     <t xml:space="preserve">8, 3, 12</t>
   </si>
   <si>
     <t xml:space="preserve">1701973735500640_231207_132857_round1</t>
   </si>
   <si>
+    <t xml:space="preserve">231207_round1</t>
+  </si>
+  <si>
     <t xml:space="preserve">13, 12, 22, 11, 3, 27, 9 , 31, 28, 29</t>
   </si>
   <si>
     <t xml:space="preserve">1701976043324504_231207_140723_round2</t>
   </si>
   <si>
+    <t xml:space="preserve">231207_round2</t>
+  </si>
+  <si>
     <t xml:space="preserve">27, 4, 9, 22, 29, 13, 18, 19, 11</t>
   </si>
   <si>
     <t xml:space="preserve">1701978176532798_231207_144257_round3</t>
   </si>
   <si>
+    <t xml:space="preserve">231207_round3</t>
+  </si>
+  <si>
     <t xml:space="preserve">5, 26, 8, 23, 16</t>
   </si>
   <si>
     <t xml:space="preserve">1701980531598335_231207_152212_round4</t>
   </si>
   <si>
+    <t xml:space="preserve">231207_round4</t>
+  </si>
+  <si>
     <t xml:space="preserve">4, 12, 19, 9, 11</t>
   </si>
   <si>
     <t xml:space="preserve">1702324458607914_231211_145420_round1</t>
   </si>
   <si>
+    <t xml:space="preserve">231211_round1</t>
+  </si>
+  <si>
     <t xml:space="preserve">5, 3, 26, 4, 12, 28, 22, 20, 10</t>
   </si>
   <si>
     <t xml:space="preserve">1702326551467901_231211_152912_round2</t>
   </si>
   <si>
+    <t xml:space="preserve">231211_round2</t>
+  </si>
+  <si>
     <t xml:space="preserve">15, 1, 24, 27</t>
   </si>
   <si>
@@ -1236,6 +1329,9 @@
     <t xml:space="preserve">1702328703565086_231211_160504_round3</t>
   </si>
   <si>
+    <t xml:space="preserve">231211_round3</t>
+  </si>
+  <si>
     <t xml:space="preserve">15, 30</t>
   </si>
   <si>
@@ -1245,6 +1341,9 @@
     <t xml:space="preserve">1702330956397074_231211_164236_round4</t>
   </si>
   <si>
+    <t xml:space="preserve">231211_round4</t>
+  </si>
+  <si>
     <t xml:space="preserve">30, 0, 18, 7, 12, 1, 8, 13, 20, 24, 26</t>
   </si>
   <si>
@@ -1260,34 +1359,52 @@
     <t xml:space="preserve">1702583713264981_231214_145513_round2</t>
   </si>
   <si>
+    <t xml:space="preserve">231214_round2</t>
+  </si>
+  <si>
     <t xml:space="preserve">30, 20</t>
   </si>
   <si>
     <t xml:space="preserve">1702586528828550_231214_154209_round3</t>
   </si>
   <si>
+    <t xml:space="preserve">231214_round3</t>
+  </si>
+  <si>
     <t xml:space="preserve">30, 0, 6, 14, 13, 4, 8</t>
   </si>
   <si>
     <t xml:space="preserve">1702587195889919_231214_155316_round4</t>
   </si>
   <si>
+    <t xml:space="preserve">231214_round4</t>
+  </si>
+  <si>
     <t xml:space="preserve">1, 14, 23, 16, 8, 29</t>
   </si>
   <si>
     <t xml:space="preserve">1702932267299951_231218_154428_round1</t>
   </si>
   <si>
+    <t xml:space="preserve">231218_round1</t>
+  </si>
+  <si>
     <t xml:space="preserve">30, 17, 29, 2, 13, 12, 31</t>
   </si>
   <si>
     <t xml:space="preserve">1702935175603837_231218_163256_round2</t>
   </si>
   <si>
+    <t xml:space="preserve">231218_round2</t>
+  </si>
+  <si>
     <t xml:space="preserve">2, 20, 3, 26, 29, 21, 15</t>
   </si>
   <si>
     <t xml:space="preserve">1702937566118826_231218_171246_round3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231218_round3</t>
   </si>
   <si>
     <t xml:space="preserve">Original Channels</t>
@@ -2507,7 +2624,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B35"/>
-  <sheetFormatPr defaultColWidth="12.07421875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.42"/>
   </cols>
@@ -2765,7 +2882,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -2779,7 +2896,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q57"/>
-  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34.32"/>
@@ -2794,13 +2911,13 @@
         <v>196</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="D1" s="69" t="s">
-        <v>585</v>
+        <v>624</v>
       </c>
       <c r="E1" s="69" t="s">
-        <v>586</v>
+        <v>625</v>
       </c>
       <c r="F1" s="69" t="s">
         <v>197</v>
@@ -2808,13 +2925,13 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>2.2074101006976</v>
@@ -2823,18 +2940,18 @@
         <v>0</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>460</v>
+        <v>499</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>1.91618820713828</v>
@@ -2843,18 +2960,18 @@
         <v>0.005</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>461</v>
+        <v>500</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>2.1549031694575</v>
@@ -2863,18 +2980,18 @@
         <v>0.001</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>1.63436939913336</v>
@@ -2883,18 +3000,18 @@
         <v>0.017</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>466</v>
+        <v>505</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>1.50610213394371</v>
@@ -2903,18 +3020,18 @@
         <v>0.039</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>2.14014139185557</v>
@@ -2923,18 +3040,18 @@
         <v>0</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>1.77118649519716</v>
@@ -2943,18 +3060,18 @@
         <v>0.007</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>469</v>
+        <v>508</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>2.72723767707481</v>
@@ -2963,18 +3080,18 @@
         <v>0</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>471</v>
+        <v>510</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>1.69976597148251</v>
@@ -2983,18 +3100,18 @@
         <v>0.008</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>470</v>
+        <v>509</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>1.5901745302229</v>
@@ -3003,18 +3120,18 @@
         <v>0.02</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>4.02906159821023</v>
@@ -3023,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="I12" s="70"/>
       <c r="J12" s="70"/>
@@ -3037,13 +3154,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>472</v>
+        <v>511</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>1.76777113757494</v>
@@ -3052,18 +3169,18 @@
         <v>0.009</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>474</v>
+        <v>513</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>1.63185608974999</v>
@@ -3072,18 +3189,18 @@
         <v>0.013</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>1.52138947807465</v>
@@ -3092,18 +3209,18 @@
         <v>0.029</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>475</v>
+        <v>514</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>1.6793716821355</v>
@@ -3112,18 +3229,18 @@
         <v>0.009</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>478</v>
+        <v>517</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>2.54515787946982</v>
@@ -3132,18 +3249,18 @@
         <v>0</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>477</v>
+        <v>516</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>4.01472539945866</v>
@@ -3152,18 +3269,18 @@
         <v>0</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>480</v>
+        <v>519</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>1.79469654146809</v>
@@ -3172,18 +3289,18 @@
         <v>0.008</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>521</v>
+        <v>560</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>1.44724614904559</v>
@@ -3192,18 +3309,18 @@
         <v>0.048</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>483</v>
+        <v>522</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>2.84117212159127</v>
@@ -3212,18 +3329,18 @@
         <v>0</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>481</v>
+        <v>520</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>2.62176931171978</v>
@@ -3232,18 +3349,18 @@
         <v>0</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>479</v>
+        <v>518</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>1.60624558373243</v>
@@ -3252,18 +3369,18 @@
         <v>0.02</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>2.50231791941221</v>
@@ -3272,18 +3389,18 @@
         <v>0</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>461</v>
+        <v>500</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>2.38119735532425</v>
@@ -3292,18 +3409,18 @@
         <v>0</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>1.99897224402669</v>
@@ -3312,18 +3429,18 @@
         <v>0</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>485</v>
+        <v>524</v>
       </c>
       <c r="D27" s="0" t="n">
         <v>1.67433985036413</v>
@@ -3332,18 +3449,18 @@
         <v>0.008</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>484</v>
+        <v>523</v>
       </c>
       <c r="D28" s="0" t="n">
         <v>1.94692117037371</v>
@@ -3352,18 +3469,18 @@
         <v>0.001</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="D29" s="0" t="n">
         <v>1.48771520027684</v>
@@ -3372,18 +3489,18 @@
         <v>0.043</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>487</v>
+        <v>526</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>488</v>
+        <v>527</v>
       </c>
       <c r="D30" s="0" t="n">
         <v>1.70880387185988</v>
@@ -3392,18 +3509,18 @@
         <v>0.004</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="D31" s="0" t="n">
         <v>1.45808984198919</v>
@@ -3412,18 +3529,18 @@
         <v>0.038</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="D32" s="0" t="n">
         <v>1.48586965365735</v>
@@ -3432,18 +3549,18 @@
         <v>0.048</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="D33" s="0" t="n">
         <v>1.87671517502119</v>
@@ -3452,18 +3569,18 @@
         <v>0</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="D34" s="0" t="n">
         <v>1.60512687967736</v>
@@ -3472,18 +3589,18 @@
         <v>0.017</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>493</v>
+        <v>532</v>
       </c>
       <c r="D35" s="0" t="n">
         <v>1.5812425577225</v>
@@ -3492,18 +3609,18 @@
         <v>0.021</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="D36" s="0" t="n">
         <v>2.08130121573154</v>
@@ -3512,18 +3629,18 @@
         <v>0.001</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>498</v>
+        <v>537</v>
       </c>
       <c r="D37" s="0" t="n">
         <v>1.58539177480019</v>
@@ -3537,13 +3654,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="D38" s="0" t="n">
         <v>2.87319933443605</v>
@@ -3557,13 +3674,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B39" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="D39" s="0" t="n">
         <v>2.63965164315008</v>
@@ -3577,13 +3694,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="D40" s="0" t="n">
         <v>1.56015382198044</v>
@@ -3597,13 +3714,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>500</v>
+        <v>539</v>
       </c>
       <c r="D41" s="0" t="n">
         <v>2.34192597660081</v>
@@ -3617,13 +3734,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="D42" s="0" t="n">
         <v>1.71588161330883</v>
@@ -3637,13 +3754,13 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B43" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="D43" s="0" t="n">
         <v>1.60345746172396</v>
@@ -3657,13 +3774,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="D44" s="0" t="n">
         <v>1.77279484716295</v>
@@ -3677,13 +3794,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="D45" s="0" t="n">
         <v>1.46904572168543</v>
@@ -3697,13 +3814,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>587</v>
+        <v>626</v>
       </c>
       <c r="D46" s="0" t="n">
         <v>1.44718215811966</v>
@@ -3717,13 +3834,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="B47" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="D47" s="0" t="n">
         <v>1.5465047856784</v>
@@ -3737,13 +3854,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="D48" s="0" t="n">
         <v>1.6694769037473</v>
@@ -3757,13 +3874,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>506</v>
+        <v>545</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>507</v>
+        <v>546</v>
       </c>
       <c r="D49" s="0" t="n">
         <v>1.80825978905348</v>
@@ -3777,13 +3894,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>506</v>
+        <v>545</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>508</v>
+        <v>547</v>
       </c>
       <c r="D50" s="0" t="n">
         <v>1.50702991416818</v>
@@ -3797,13 +3914,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>506</v>
+        <v>545</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="D51" s="0" t="n">
         <v>1.64248173240046</v>
@@ -3817,13 +3934,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>475</v>
+        <v>514</v>
       </c>
       <c r="D52" s="0" t="n">
         <v>1.67112657224445</v>
@@ -3837,13 +3954,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>510</v>
+        <v>549</v>
       </c>
       <c r="D53" s="0" t="n">
         <v>1.52503810145874</v>
@@ -3857,13 +3974,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>511</v>
+        <v>550</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>512</v>
+        <v>551</v>
       </c>
       <c r="D54" s="0" t="n">
         <v>1.83132158328407</v>
@@ -3877,13 +3994,13 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="D55" s="0" t="n">
         <v>1.70084982084048</v>
@@ -3897,13 +4014,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
       <c r="D56" s="0" t="n">
         <v>1.7452039589713</v>
@@ -3917,13 +4034,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>512</v>
+        <v>551</v>
       </c>
       <c r="D57" s="0" t="n">
         <v>1.50025155234275</v>
@@ -3938,7 +4055,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -3952,22 +4069,22 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>205</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>588</v>
+        <v>627</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>589</v>
+        <v>628</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>37</v>
@@ -3981,7 +4098,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>590</v>
+        <v>629</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>26</v>
@@ -3992,7 +4109,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>591</v>
+        <v>630</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>35</v>
@@ -4007,7 +4124,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -4021,7 +4138,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H121"/>
-  <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="14.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.92"/>
@@ -4039,13 +4156,13 @@
         <v>196</v>
       </c>
       <c r="C1" s="65" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>592</v>
+        <v>631</v>
       </c>
       <c r="E1" s="65" t="s">
-        <v>593</v>
+        <v>632</v>
       </c>
       <c r="F1" s="66" t="s">
         <v>197</v>
@@ -4054,7 +4171,7 @@
         <v>62</v>
       </c>
       <c r="H1" s="66" t="s">
-        <v>594</v>
+        <v>633</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4065,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>0</v>
@@ -4074,7 +4191,7 @@
         <v>300</v>
       </c>
       <c r="F2" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4085,7 +4202,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="72" t="s">
-        <v>595</v>
+        <v>634</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>0</v>
@@ -4094,7 +4211,7 @@
         <v>700</v>
       </c>
       <c r="F3" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4105,7 +4222,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="72" t="s">
-        <v>461</v>
+        <v>500</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>0</v>
@@ -4114,7 +4231,7 @@
         <v>2000</v>
       </c>
       <c r="F4" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4125,7 +4242,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="72" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>0</v>
@@ -4134,7 +4251,7 @@
         <v>400</v>
       </c>
       <c r="F5" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4145,7 +4262,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="72" t="s">
-        <v>596</v>
+        <v>635</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>250</v>
@@ -4154,7 +4271,7 @@
         <v>750</v>
       </c>
       <c r="F6" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4165,7 +4282,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="72" t="s">
-        <v>556</v>
+        <v>595</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>100</v>
@@ -4174,7 +4291,7 @@
         <v>350</v>
       </c>
       <c r="F7" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4185,7 +4302,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>150</v>
@@ -4194,7 +4311,7 @@
         <v>650</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4205,7 +4322,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>597</v>
+        <v>636</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>400</v>
@@ -4214,7 +4331,7 @@
         <v>1000</v>
       </c>
       <c r="F9" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4225,7 +4342,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="72" t="s">
-        <v>598</v>
+        <v>637</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>200</v>
@@ -4234,7 +4351,7 @@
         <v>600</v>
       </c>
       <c r="F10" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4245,7 +4362,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="72" t="s">
-        <v>558</v>
+        <v>597</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>0</v>
@@ -4254,7 +4371,7 @@
         <v>250</v>
       </c>
       <c r="F11" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4265,7 +4382,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="72" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>0</v>
@@ -4274,7 +4391,7 @@
         <v>600</v>
       </c>
       <c r="F12" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4285,7 +4402,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="72" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>200</v>
@@ -4294,7 +4411,7 @@
         <v>600</v>
       </c>
       <c r="F13" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4305,7 +4422,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="72" t="s">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>150</v>
@@ -4314,7 +4431,7 @@
         <v>750</v>
       </c>
       <c r="F14" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4325,7 +4442,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="72" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>150</v>
@@ -4334,7 +4451,7 @@
         <v>750</v>
       </c>
       <c r="F15" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4345,7 +4462,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="72" t="s">
-        <v>477</v>
+        <v>516</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>100</v>
@@ -4354,7 +4471,7 @@
         <v>700</v>
       </c>
       <c r="F16" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4365,7 +4482,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="72" t="s">
-        <v>600</v>
+        <v>639</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>400</v>
@@ -4374,7 +4491,7 @@
         <v>1000</v>
       </c>
       <c r="F17" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4385,7 +4502,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="72" t="s">
-        <v>478</v>
+        <v>517</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>100</v>
@@ -4394,7 +4511,7 @@
         <v>500</v>
       </c>
       <c r="F18" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4405,7 +4522,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="72" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>100</v>
@@ -4414,7 +4531,7 @@
         <v>500</v>
       </c>
       <c r="F19" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4425,7 +4542,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="72" t="s">
-        <v>481</v>
+        <v>520</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>100</v>
@@ -4434,7 +4551,7 @@
         <v>500</v>
       </c>
       <c r="F20" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4445,7 +4562,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="72" t="s">
-        <v>480</v>
+        <v>519</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>0</v>
@@ -4454,7 +4571,7 @@
         <v>2000</v>
       </c>
       <c r="F21" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4465,7 +4582,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="72" t="s">
-        <v>483</v>
+        <v>522</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>0</v>
@@ -4474,7 +4591,7 @@
         <v>2000</v>
       </c>
       <c r="F22" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4485,7 +4602,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="72" t="s">
-        <v>479</v>
+        <v>518</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>0</v>
@@ -4494,7 +4611,7 @@
         <v>500</v>
       </c>
       <c r="F23" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4505,7 +4622,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="72" t="s">
-        <v>461</v>
+        <v>500</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>0</v>
@@ -4514,7 +4631,7 @@
         <v>500</v>
       </c>
       <c r="F24" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4525,7 +4642,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="72" t="s">
-        <v>597</v>
+        <v>636</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>0</v>
@@ -4534,7 +4651,7 @@
         <v>500</v>
       </c>
       <c r="F25" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4545,7 +4662,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="72" t="s">
-        <v>601</v>
+        <v>640</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>0</v>
@@ -4554,7 +4671,7 @@
         <v>2000</v>
       </c>
       <c r="F26" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4565,7 +4682,7 @@
         <v>3</v>
       </c>
       <c r="C27" s="72" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="D27" s="0" t="n">
         <v>0</v>
@@ -4574,7 +4691,7 @@
         <v>2000</v>
       </c>
       <c r="F27" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4585,7 +4702,7 @@
         <v>3</v>
       </c>
       <c r="C28" s="72" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="D28" s="0" t="n">
         <v>0</v>
@@ -4594,7 +4711,7 @@
         <v>700</v>
       </c>
       <c r="F28" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4605,7 +4722,7 @@
         <v>3</v>
       </c>
       <c r="C29" s="72" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="D29" s="0" t="n">
         <v>700</v>
@@ -4614,7 +4731,7 @@
         <v>2000</v>
       </c>
       <c r="F29" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4625,7 +4742,7 @@
         <v>4</v>
       </c>
       <c r="C30" s="72" t="s">
-        <v>603</v>
+        <v>642</v>
       </c>
       <c r="D30" s="0" t="n">
         <v>0</v>
@@ -4634,7 +4751,7 @@
         <v>700</v>
       </c>
       <c r="F30" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4645,7 +4762,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="72" t="s">
-        <v>488</v>
+        <v>527</v>
       </c>
       <c r="D31" s="0" t="n">
         <v>0</v>
@@ -4654,7 +4771,7 @@
         <v>700</v>
       </c>
       <c r="F31" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4665,7 +4782,7 @@
         <v>4</v>
       </c>
       <c r="C32" s="72" t="s">
-        <v>484</v>
+        <v>523</v>
       </c>
       <c r="D32" s="0" t="n">
         <v>0</v>
@@ -4674,7 +4791,7 @@
         <v>700</v>
       </c>
       <c r="F32" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4685,7 +4802,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="72" t="s">
-        <v>565</v>
+        <v>604</v>
       </c>
       <c r="D33" s="0" t="n">
         <v>0</v>
@@ -4694,7 +4811,7 @@
         <v>750</v>
       </c>
       <c r="F33" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4705,7 +4822,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="72" t="s">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="D34" s="0" t="n">
         <v>250</v>
@@ -4714,7 +4831,7 @@
         <v>750</v>
       </c>
       <c r="F34" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4725,7 +4842,7 @@
         <v>4</v>
       </c>
       <c r="C35" s="72" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="D35" s="0" t="n">
         <v>250</v>
@@ -4734,7 +4851,7 @@
         <v>750</v>
       </c>
       <c r="F35" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4745,7 +4862,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="72" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="D36" s="0" t="n">
         <v>0</v>
@@ -4754,7 +4871,7 @@
         <v>2000</v>
       </c>
       <c r="F36" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4765,7 +4882,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="72" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="D37" s="0" t="n">
         <v>0</v>
@@ -4774,7 +4891,7 @@
         <v>2000</v>
       </c>
       <c r="F37" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4785,7 +4902,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="72" t="s">
-        <v>587</v>
+        <v>626</v>
       </c>
       <c r="D38" s="0" t="n">
         <v>0</v>
@@ -4794,7 +4911,7 @@
         <v>2000</v>
       </c>
       <c r="F38" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4805,7 +4922,7 @@
         <v>3</v>
       </c>
       <c r="C39" s="72" t="s">
-        <v>604</v>
+        <v>643</v>
       </c>
       <c r="D39" s="0" t="n">
         <v>0</v>
@@ -4814,10 +4931,10 @@
         <v>2000</v>
       </c>
       <c r="F39" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4828,7 +4945,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="72" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="D40" s="0" t="n">
         <v>0</v>
@@ -4837,7 +4954,7 @@
         <v>600</v>
       </c>
       <c r="F40" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4848,7 +4965,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="72" t="s">
-        <v>562</v>
+        <v>601</v>
       </c>
       <c r="D41" s="0" t="n">
         <v>200</v>
@@ -4857,7 +4974,7 @@
         <v>700</v>
       </c>
       <c r="F41" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4868,7 +4985,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="72" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="D42" s="0" t="s">
         <v>64</v>
@@ -4877,10 +4994,10 @@
         <v>64</v>
       </c>
       <c r="F42" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4891,7 +5008,7 @@
         <v>2</v>
       </c>
       <c r="C43" s="72" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="D43" s="0" t="n">
         <v>200</v>
@@ -4900,7 +5017,7 @@
         <v>700</v>
       </c>
       <c r="F43" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4911,7 +5028,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="72" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="D44" s="0" t="n">
         <v>250</v>
@@ -4920,7 +5037,7 @@
         <v>750</v>
       </c>
       <c r="F44" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4931,7 +5048,7 @@
         <v>3</v>
       </c>
       <c r="C45" s="72" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="D45" s="0" t="n">
         <v>0</v>
@@ -4940,7 +5057,7 @@
         <v>2000</v>
       </c>
       <c r="F45" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4951,7 +5068,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="72" t="s">
-        <v>508</v>
+        <v>547</v>
       </c>
       <c r="D46" s="0" t="n">
         <v>250</v>
@@ -4960,7 +5077,7 @@
         <v>750</v>
       </c>
       <c r="F46" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4971,7 +5088,7 @@
         <v>1</v>
       </c>
       <c r="C47" s="72" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="D47" s="0" t="n">
         <v>100</v>
@@ -4980,7 +5097,7 @@
         <v>500</v>
       </c>
       <c r="F47" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4991,7 +5108,7 @@
         <v>1</v>
       </c>
       <c r="C48" s="72" t="s">
-        <v>562</v>
+        <v>601</v>
       </c>
       <c r="D48" s="0" t="n">
         <v>250</v>
@@ -5000,7 +5117,7 @@
         <v>750</v>
       </c>
       <c r="F48" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5011,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="D49" s="0" t="n">
         <v>0</v>
@@ -5020,7 +5137,7 @@
         <v>2000</v>
       </c>
       <c r="F49" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5031,7 +5148,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
       <c r="D50" s="0" t="s">
         <v>64</v>
@@ -5040,10 +5157,10 @@
         <v>64</v>
       </c>
       <c r="F50" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5054,7 +5171,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="D51" s="0" t="n">
         <v>250</v>
@@ -5063,7 +5180,7 @@
         <v>750</v>
       </c>
       <c r="F51" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5074,7 +5191,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>604</v>
+        <v>643</v>
       </c>
       <c r="D52" s="0" t="n">
         <v>0</v>
@@ -5083,10 +5200,10 @@
         <v>2000</v>
       </c>
       <c r="F52" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5097,7 +5214,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="D53" s="0" t="n">
         <v>0</v>
@@ -5106,10 +5223,10 @@
         <v>2000</v>
       </c>
       <c r="F53" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5120,7 +5237,7 @@
         <v>2</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="D54" s="0" t="n">
         <v>250</v>
@@ -5140,7 +5257,7 @@
         <v>2</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>587</v>
+        <v>626</v>
       </c>
       <c r="D55" s="0" t="s">
         <v>64</v>
@@ -5152,7 +5269,7 @@
         <v>205</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5163,7 +5280,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>606</v>
+        <v>645</v>
       </c>
       <c r="D56" s="0" t="s">
         <v>64</v>
@@ -5172,13 +5289,13 @@
         <v>64</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>607</v>
+        <v>646</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5189,7 +5306,7 @@
         <v>1</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="D57" s="0" t="s">
         <v>64</v>
@@ -5198,13 +5315,13 @@
         <v>64</v>
       </c>
       <c r="F57" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>607</v>
+        <v>646</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5215,7 +5332,7 @@
         <v>1</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="D58" s="0" t="s">
         <v>64</v>
@@ -5224,13 +5341,13 @@
         <v>64</v>
       </c>
       <c r="F58" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>607</v>
+        <v>646</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5241,7 +5358,7 @@
         <v>4</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>498</v>
+        <v>537</v>
       </c>
       <c r="D59" s="0" t="n">
         <v>0</v>
@@ -5261,7 +5378,7 @@
         <v>4</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>608</v>
+        <v>647</v>
       </c>
       <c r="D60" s="0" t="n">
         <v>0</v>
@@ -5281,7 +5398,7 @@
         <v>4</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="D61" s="0" t="n">
         <v>0</v>
@@ -5301,7 +5418,7 @@
         <v>4</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>609</v>
+        <v>648</v>
       </c>
       <c r="D62" s="0" t="n">
         <v>250</v>
@@ -5321,7 +5438,7 @@
         <v>4</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="D63" s="0" t="n">
         <v>0</v>
@@ -5341,7 +5458,7 @@
         <v>4</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>500</v>
+        <v>539</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>64</v>
@@ -5353,7 +5470,7 @@
         <v>205</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5364,7 +5481,7 @@
         <v>1</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="D65" s="0" t="n">
         <v>0</v>
@@ -5384,7 +5501,7 @@
         <v>1</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>460</v>
+        <v>499</v>
       </c>
       <c r="D66" s="0" t="n">
         <v>250</v>
@@ -5404,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="D67" s="0" t="n">
         <v>100</v>
@@ -5424,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="D68" s="0" t="s">
         <v>64</v>
@@ -5436,7 +5553,7 @@
         <v>210</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5447,7 +5564,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="D69" s="0" t="n">
         <v>100</v>
@@ -5467,7 +5584,7 @@
         <v>1</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>493</v>
+        <v>532</v>
       </c>
       <c r="D70" s="0" t="n">
         <v>0</v>
@@ -5487,7 +5604,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>610</v>
+        <v>649</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>64</v>
@@ -5499,7 +5616,7 @@
         <v>210</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5510,7 +5627,7 @@
         <v>2</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>606</v>
+        <v>645</v>
       </c>
       <c r="D72" s="0" t="n">
         <v>0</v>
@@ -5530,7 +5647,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>606</v>
+        <v>645</v>
       </c>
       <c r="D73" s="0" t="n">
         <v>1250</v>
@@ -5550,7 +5667,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="D74" s="0" t="n">
         <v>100</v>
@@ -5570,7 +5687,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>609</v>
+        <v>648</v>
       </c>
       <c r="D75" s="0" t="n">
         <v>0</v>
@@ -5590,7 +5707,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>493</v>
+        <v>532</v>
       </c>
       <c r="D76" s="0" t="n">
         <v>0</v>
@@ -5610,7 +5727,7 @@
         <v>2</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="D77" s="0" t="n">
         <v>250</v>
@@ -5622,7 +5739,7 @@
         <v>210</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5633,7 +5750,7 @@
         <v>1</v>
       </c>
       <c r="C78" s="72" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="D78" s="0" t="n">
         <v>100</v>
@@ -5653,7 +5770,7 @@
         <v>1</v>
       </c>
       <c r="C79" s="72" t="s">
-        <v>604</v>
+        <v>643</v>
       </c>
       <c r="D79" s="0" t="s">
         <v>64</v>
@@ -5665,7 +5782,7 @@
         <v>210</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5676,7 +5793,7 @@
         <v>2</v>
       </c>
       <c r="C80" s="72" t="s">
-        <v>606</v>
+        <v>645</v>
       </c>
       <c r="D80" s="0" t="n">
         <v>0</v>
@@ -5696,7 +5813,7 @@
         <v>2</v>
       </c>
       <c r="C81" s="72" t="s">
-        <v>606</v>
+        <v>645</v>
       </c>
       <c r="D81" s="0" t="n">
         <v>250</v>
@@ -5716,7 +5833,7 @@
         <v>2</v>
       </c>
       <c r="C82" s="72" t="s">
-        <v>609</v>
+        <v>648</v>
       </c>
       <c r="D82" s="0" t="n">
         <v>0</v>
@@ -5736,7 +5853,7 @@
         <v>2</v>
       </c>
       <c r="C83" s="72" t="s">
-        <v>609</v>
+        <v>648</v>
       </c>
       <c r="D83" s="0" t="n">
         <v>250</v>
@@ -5756,7 +5873,7 @@
         <v>2</v>
       </c>
       <c r="C84" s="72" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="D84" s="0" t="n">
         <v>200</v>
@@ -5776,7 +5893,7 @@
         <v>2</v>
       </c>
       <c r="C85" s="72" t="s">
-        <v>508</v>
+        <v>547</v>
       </c>
       <c r="D85" s="0" t="s">
         <v>64</v>
@@ -5788,7 +5905,7 @@
         <v>210</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5799,7 +5916,7 @@
         <v>3</v>
       </c>
       <c r="C86" s="72" t="s">
-        <v>606</v>
+        <v>645</v>
       </c>
       <c r="D86" s="0" t="n">
         <v>0</v>
@@ -5819,7 +5936,7 @@
         <v>3</v>
       </c>
       <c r="C87" s="72" t="s">
-        <v>606</v>
+        <v>645</v>
       </c>
       <c r="D87" s="0" t="n">
         <v>250</v>
@@ -5839,7 +5956,7 @@
         <v>3</v>
       </c>
       <c r="C88" s="72" t="s">
-        <v>606</v>
+        <v>645</v>
       </c>
       <c r="D88" s="0" t="n">
         <v>1250</v>
@@ -5859,7 +5976,7 @@
         <v>3</v>
       </c>
       <c r="C89" s="72" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="D89" s="0" t="n">
         <v>250</v>
@@ -5879,7 +5996,7 @@
         <v>3</v>
       </c>
       <c r="C90" s="72" t="s">
-        <v>611</v>
+        <v>650</v>
       </c>
       <c r="D90" s="0" t="n">
         <v>0</v>
@@ -5899,7 +6016,7 @@
         <v>3</v>
       </c>
       <c r="C91" s="72" t="s">
-        <v>611</v>
+        <v>650</v>
       </c>
       <c r="D91" s="0" t="n">
         <v>250</v>
@@ -5919,7 +6036,7 @@
         <v>3</v>
       </c>
       <c r="C92" s="72" t="s">
-        <v>609</v>
+        <v>648</v>
       </c>
       <c r="D92" s="0" t="n">
         <v>0</v>
@@ -5939,7 +6056,7 @@
         <v>3</v>
       </c>
       <c r="C93" s="72" t="s">
-        <v>609</v>
+        <v>648</v>
       </c>
       <c r="D93" s="0" t="n">
         <v>250</v>
@@ -5959,7 +6076,7 @@
         <v>3</v>
       </c>
       <c r="C94" s="72" t="s">
-        <v>609</v>
+        <v>648</v>
       </c>
       <c r="D94" s="0" t="n">
         <v>1000</v>
@@ -5979,7 +6096,7 @@
         <v>4</v>
       </c>
       <c r="C95" s="72" t="s">
-        <v>612</v>
+        <v>651</v>
       </c>
       <c r="D95" s="0" t="n">
         <v>250</v>
@@ -5999,7 +6116,7 @@
         <v>1</v>
       </c>
       <c r="C96" s="72" t="s">
-        <v>498</v>
+        <v>537</v>
       </c>
       <c r="D96" s="0" t="n">
         <v>250</v>
@@ -6019,7 +6136,7 @@
         <v>2</v>
       </c>
       <c r="C97" s="72" t="s">
-        <v>611</v>
+        <v>650</v>
       </c>
       <c r="D97" s="0" t="n">
         <v>100</v>
@@ -6039,7 +6156,7 @@
         <v>2</v>
       </c>
       <c r="C98" s="72" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="D98" s="0" t="n">
         <v>100</v>
@@ -6059,7 +6176,7 @@
         <v>2</v>
       </c>
       <c r="C99" s="72" t="s">
-        <v>493</v>
+        <v>532</v>
       </c>
       <c r="D99" s="0" t="n">
         <v>250</v>
@@ -6071,7 +6188,7 @@
         <v>205</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6082,7 +6199,7 @@
         <v>2</v>
       </c>
       <c r="C100" s="72" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="D100" s="0" t="n">
         <v>250</v>
@@ -6102,7 +6219,7 @@
         <v>2</v>
       </c>
       <c r="C101" s="72" t="s">
-        <v>575</v>
+        <v>614</v>
       </c>
       <c r="D101" s="0" t="n">
         <v>200</v>
@@ -6114,7 +6231,7 @@
         <v>205</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6125,7 +6242,7 @@
         <v>3</v>
       </c>
       <c r="C102" s="72" t="s">
-        <v>575</v>
+        <v>614</v>
       </c>
       <c r="D102" s="0" t="n">
         <v>250</v>
@@ -6145,7 +6262,7 @@
         <v>2</v>
       </c>
       <c r="C103" s="72" t="s">
-        <v>498</v>
+        <v>537</v>
       </c>
       <c r="D103" s="0" t="n">
         <v>100</v>
@@ -6165,7 +6282,7 @@
         <v>2</v>
       </c>
       <c r="C104" s="72" t="s">
-        <v>604</v>
+        <v>643</v>
       </c>
       <c r="D104" s="0" t="n">
         <v>200</v>
@@ -6185,7 +6302,7 @@
         <v>2</v>
       </c>
       <c r="C105" s="72" t="s">
-        <v>507</v>
+        <v>546</v>
       </c>
       <c r="D105" s="0" t="n">
         <v>200</v>
@@ -6205,7 +6322,7 @@
         <v>3</v>
       </c>
       <c r="C106" s="72" t="s">
-        <v>604</v>
+        <v>643</v>
       </c>
       <c r="D106" s="0" t="n">
         <v>300</v>
@@ -6225,7 +6342,7 @@
         <v>1</v>
       </c>
       <c r="C107" s="72" t="s">
-        <v>498</v>
+        <v>537</v>
       </c>
       <c r="D107" s="0" t="s">
         <v>64</v>
@@ -6237,7 +6354,7 @@
         <v>210</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6248,7 +6365,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="72" t="s">
-        <v>608</v>
+        <v>647</v>
       </c>
       <c r="D108" s="0" t="n">
         <v>0</v>
@@ -6268,7 +6385,7 @@
         <v>1</v>
       </c>
       <c r="C109" s="72" t="s">
-        <v>612</v>
+        <v>651</v>
       </c>
       <c r="D109" s="0" t="n">
         <v>100</v>
@@ -6288,7 +6405,7 @@
         <v>1</v>
       </c>
       <c r="C110" s="72" t="s">
-        <v>512</v>
+        <v>551</v>
       </c>
       <c r="D110" s="0" t="n">
         <v>100</v>
@@ -6300,7 +6417,7 @@
         <v>210</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6311,7 +6428,7 @@
         <v>2</v>
       </c>
       <c r="C111" s="72" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="D111" s="0" t="n">
         <v>0</v>
@@ -6331,7 +6448,7 @@
         <v>2</v>
       </c>
       <c r="C112" s="72" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
       <c r="D112" s="0" t="n">
         <v>0</v>
@@ -6343,7 +6460,7 @@
         <v>210</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6354,7 +6471,7 @@
         <v>2</v>
       </c>
       <c r="C113" s="72" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="D113" s="0" t="n">
         <v>0</v>
@@ -6374,7 +6491,7 @@
         <v>2</v>
       </c>
       <c r="C114" s="72" t="s">
-        <v>562</v>
+        <v>601</v>
       </c>
       <c r="D114" s="0" t="n">
         <v>0</v>
@@ -6394,7 +6511,7 @@
         <v>2</v>
       </c>
       <c r="C115" s="72" t="s">
-        <v>611</v>
+        <v>650</v>
       </c>
       <c r="D115" s="0" t="s">
         <v>64</v>
@@ -6406,7 +6523,7 @@
         <v>210</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6417,7 +6534,7 @@
         <v>2</v>
       </c>
       <c r="C116" s="72" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="D116" s="0" t="n">
         <v>0</v>
@@ -6437,7 +6554,7 @@
         <v>2</v>
       </c>
       <c r="C117" s="72" t="s">
-        <v>610</v>
+        <v>649</v>
       </c>
       <c r="D117" s="0" t="n">
         <v>0</v>
@@ -6449,7 +6566,7 @@
         <v>210</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>613</v>
+        <v>652</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6460,7 +6577,7 @@
         <v>2</v>
       </c>
       <c r="C118" s="72" t="s">
-        <v>610</v>
+        <v>649</v>
       </c>
       <c r="D118" s="0" t="n">
         <v>1000</v>
@@ -6472,7 +6589,7 @@
         <v>210</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>613</v>
+        <v>652</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6483,7 +6600,7 @@
         <v>1</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="D119" s="0" t="s">
         <v>64</v>
@@ -6495,7 +6612,7 @@
         <v>210</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6506,7 +6623,7 @@
         <v>2</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="D120" s="0" t="s">
         <v>64</v>
@@ -6518,7 +6635,7 @@
         <v>210</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6529,7 +6646,7 @@
         <v>2</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
       <c r="D121" s="0" t="s">
         <v>64</v>
@@ -6541,13 +6658,13 @@
         <v>210</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -6561,7 +6678,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="45.11"/>
   </cols>
@@ -6574,7 +6691,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="72" t="s">
-        <v>500</v>
+        <v>539</v>
       </c>
       <c r="D1" s="0" t="n">
         <v>250</v>
@@ -6583,16 +6700,16 @@
         <v>750</v>
       </c>
       <c r="F1" s="72" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -6606,7 +6723,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.23"/>
@@ -6621,13 +6738,13 @@
         <v>196</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>614</v>
+        <v>653</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>615</v>
+        <v>654</v>
       </c>
       <c r="F1" s="0" t="s">
         <v>197</v>
@@ -6641,16 +6758,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>616</v>
+        <v>655</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="E2" s="0" t="n">
         <v>0.030965715390678</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6661,16 +6778,16 @@
         <v>3</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>617</v>
+        <v>656</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>461</v>
+        <v>500</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>0.0001048561426</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6681,16 +6798,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>618</v>
+        <v>657</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>598</v>
+        <v>637</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>0.03527854547184</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6701,16 +6818,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>618</v>
+        <v>657</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>0.000378311542831</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6721,16 +6838,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>619</v>
+        <v>658</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>477</v>
+        <v>516</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>1.05830081034659E-006</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6741,16 +6858,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>620</v>
+        <v>659</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>478</v>
+        <v>517</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>2.13976612550698E-005</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6761,16 +6878,16 @@
         <v>2</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>620</v>
+        <v>659</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>481</v>
+        <v>520</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>7.55699317281293E-011</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6781,16 +6898,16 @@
         <v>2</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>617</v>
+        <v>656</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>483</v>
+        <v>522</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>1.66280772505988E-005</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6801,16 +6918,16 @@
         <v>3</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>621</v>
+        <v>660</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>461</v>
+        <v>500</v>
       </c>
       <c r="E10" s="0" t="n">
         <v>2.33114874428906E-005</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6821,16 +6938,16 @@
         <v>3</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>621</v>
+        <v>660</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>597</v>
+        <v>636</v>
       </c>
       <c r="E11" s="0" t="n">
         <v>0.012545428798116</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6841,16 +6958,16 @@
         <v>3</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>617</v>
+        <v>656</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="E12" s="0" t="n">
         <v>0.038781460115805</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6861,16 +6978,16 @@
         <v>3</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>622</v>
+        <v>661</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>0.042377881281726</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6881,16 +6998,16 @@
         <v>4</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>623</v>
+        <v>662</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>565</v>
+        <v>604</v>
       </c>
       <c r="E14" s="0" t="n">
         <v>0.011944886356068</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6901,16 +7018,16 @@
         <v>4</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>624</v>
+        <v>663</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="E15" s="0" t="n">
         <v>0.00029232953002</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6921,16 +7038,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>617</v>
+        <v>656</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="E16" s="0" t="n">
         <v>0.00986766757997</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6941,16 +7058,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>620</v>
+        <v>659</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="E17" s="0" t="n">
         <v>1.49682454822413E-005</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6961,16 +7078,16 @@
         <v>3</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>617</v>
+        <v>656</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="E18" s="0" t="n">
         <v>0.009555414268796</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6981,16 +7098,16 @@
         <v>3</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>617</v>
+        <v>656</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>604</v>
+        <v>643</v>
       </c>
       <c r="E19" s="0" t="n">
         <v>0.001540377255957</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7001,10 +7118,10 @@
         <v>2</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>624</v>
+        <v>663</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="E20" s="0" t="n">
         <v>0.01126620279013</v>
@@ -7021,10 +7138,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>623</v>
+        <v>662</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="E21" s="0" t="n">
         <v>0.006289624603342</v>
@@ -7041,10 +7158,10 @@
         <v>4</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>623</v>
+        <v>662</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="E22" s="0" t="n">
         <v>0.006514719781525</v>
@@ -7061,10 +7178,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>625</v>
+        <v>664</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>460</v>
+        <v>499</v>
       </c>
       <c r="E23" s="0" t="n">
         <v>0.004480491399968</v>
@@ -7081,10 +7198,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>626</v>
+        <v>665</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="E24" s="0" t="n">
         <v>0.011429781534636</v>
@@ -7101,10 +7218,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>619</v>
+        <v>658</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="E25" s="0" t="n">
         <v>0.000335148307695</v>
@@ -7119,7 +7236,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -7133,7 +7250,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.53"/>
@@ -7149,13 +7266,13 @@
         <v>196</v>
       </c>
       <c r="C1" s="65" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>592</v>
+        <v>631</v>
       </c>
       <c r="E1" s="65" t="s">
-        <v>593</v>
+        <v>632</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7166,7 +7283,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>521</v>
+        <v>560</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>0</v>
@@ -7183,7 +7300,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="72" t="s">
-        <v>627</v>
+        <v>666</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>0</v>
@@ -7200,7 +7317,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>558</v>
+        <v>597</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>100</v>
@@ -7217,7 +7334,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>556</v>
+        <v>595</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>0</v>
@@ -7234,7 +7351,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>604</v>
+        <v>643</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>500</v>
@@ -7251,7 +7368,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>0</v>
@@ -7268,7 +7385,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>0</v>
@@ -7285,7 +7402,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>0</v>
@@ -7302,7 +7419,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>250</v>
@@ -7319,7 +7436,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>0</v>
@@ -7336,7 +7453,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>0</v>
@@ -7353,7 +7470,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>460</v>
+        <v>499</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>250</v>
@@ -7370,7 +7487,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>460</v>
+        <v>499</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>0</v>
@@ -7387,7 +7504,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>0</v>
@@ -7404,7 +7521,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>0</v>
@@ -7421,7 +7538,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>508</v>
+        <v>547</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>250</v>
@@ -7438,7 +7555,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>0</v>
@@ -7455,7 +7572,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>508</v>
+        <v>547</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>250</v>
@@ -7472,7 +7589,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>606</v>
+        <v>645</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>0</v>
@@ -7489,7 +7606,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>0</v>
@@ -7506,7 +7623,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>587</v>
+        <v>626</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>0</v>
@@ -7523,7 +7640,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>475</v>
+        <v>514</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>0</v>
@@ -7540,7 +7657,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>250</v>
@@ -7557,7 +7674,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>0</v>
@@ -7574,7 +7691,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>0</v>
@@ -7591,7 +7708,7 @@
         <v>3</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>507</v>
+        <v>546</v>
       </c>
       <c r="D27" s="0" t="n">
         <v>0</v>
@@ -7608,7 +7725,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="D28" s="0" t="n">
         <v>0</v>
@@ -7625,7 +7742,7 @@
         <v>3</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="D29" s="0" t="n">
         <v>0</v>
@@ -7642,7 +7759,7 @@
         <v>3</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>611</v>
+        <v>650</v>
       </c>
       <c r="D30" s="0" t="n">
         <v>250</v>
@@ -7659,7 +7776,7 @@
         <v>3</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="D31" s="0" t="n">
         <v>250</v>
@@ -7676,7 +7793,7 @@
         <v>1</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>611</v>
+        <v>650</v>
       </c>
       <c r="D32" s="0" t="n">
         <v>0</v>
@@ -7693,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>533</v>
+        <v>572</v>
       </c>
       <c r="D33" s="0" t="n">
         <v>0</v>
@@ -7710,7 +7827,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>475</v>
+        <v>514</v>
       </c>
       <c r="D34" s="0" t="n">
         <v>250</v>
@@ -7727,7 +7844,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="D35" s="0" t="n">
         <v>0</v>
@@ -7745,7 +7862,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -7759,7 +7876,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="12.07421875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.86"/>
   </cols>
@@ -7988,7 +8105,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -8002,7 +8119,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H94"/>
-  <sheetFormatPr defaultColWidth="12.07421875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="9.59"/>
@@ -9701,7 +9818,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -9715,7 +9832,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D91"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.86"/>
@@ -10722,8 +10839,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -10737,7 +10854,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F91"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.42"/>
@@ -11631,7 +11748,7 @@
         <v>331</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>150</v>
+        <v>332</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11642,14 +11759,14 @@
         <v>2</v>
       </c>
       <c r="C52" s="56" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D52" s="56"/>
       <c r="E52" s="56" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>151</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11660,13 +11777,13 @@
         <v>1</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>152</v>
+        <v>338</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11677,13 +11794,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>153</v>
+        <v>341</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11694,14 +11811,14 @@
         <v>1</v>
       </c>
       <c r="C55" s="59" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D55" s="59"/>
       <c r="E55" s="59" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>154</v>
+        <v>344</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11712,14 +11829,14 @@
         <v>2</v>
       </c>
       <c r="C56" s="56" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D56" s="56"/>
       <c r="E56" s="56" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>155</v>
+        <v>347</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11730,13 +11847,13 @@
         <v>1</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>156</v>
+        <v>350</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11747,13 +11864,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>157</v>
+        <v>353</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11764,14 +11881,14 @@
         <v>1</v>
       </c>
       <c r="C59" s="59" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D59" s="59"/>
       <c r="E59" s="59" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>159</v>
+        <v>356</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11782,13 +11899,13 @@
         <v>2</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>160</v>
+        <v>359</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11799,13 +11916,13 @@
         <v>3</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>161</v>
+        <v>362</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11816,14 +11933,14 @@
         <v>4</v>
       </c>
       <c r="C62" s="56" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="D62" s="56"/>
       <c r="E62" s="56" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>162</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11834,13 +11951,13 @@
         <v>1</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>163</v>
+        <v>368</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11851,13 +11968,13 @@
         <v>2</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>164</v>
+        <v>371</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11868,13 +11985,13 @@
         <v>3</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11885,14 +12002,14 @@
         <v>1</v>
       </c>
       <c r="C66" s="59" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="D66" s="59"/>
       <c r="E66" s="59" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>167</v>
+        <v>377</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11903,13 +12020,13 @@
         <v>2</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>168</v>
+        <v>380</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11920,14 +12037,14 @@
         <v>3</v>
       </c>
       <c r="C68" s="56" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="D68" s="56"/>
       <c r="E68" s="56" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>169</v>
+        <v>383</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11938,16 +12055,16 @@
         <v>1</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>170</v>
+        <v>387</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11958,16 +12075,16 @@
         <v>2</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>171</v>
+        <v>391</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11978,13 +12095,13 @@
         <v>3</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>172</v>
+        <v>394</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11995,13 +12112,13 @@
         <v>4</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>173</v>
+        <v>397</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12012,14 +12129,14 @@
         <v>1</v>
       </c>
       <c r="C73" s="59" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="D73" s="59"/>
       <c r="E73" s="59" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>174</v>
+        <v>400</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12030,13 +12147,13 @@
         <v>2</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>175</v>
+        <v>403</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12047,13 +12164,13 @@
         <v>3</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>176</v>
+        <v>406</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12064,14 +12181,14 @@
         <v>4</v>
       </c>
       <c r="C76" s="56" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="D76" s="56"/>
       <c r="E76" s="56" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>177</v>
+        <v>409</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12082,16 +12199,16 @@
         <v>1</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="n">
         <v>45267</v>
       </c>
@@ -12099,16 +12216,16 @@
         <v>2</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="n">
         <v>45267</v>
       </c>
@@ -12116,16 +12233,16 @@
         <v>3</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="n">
         <v>45267</v>
       </c>
@@ -12133,13 +12250,13 @@
         <v>4</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>181</v>
+        <v>421</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12150,17 +12267,17 @@
         <v>1</v>
       </c>
       <c r="C81" s="59" t="s">
-        <v>393</v>
+        <v>422</v>
       </c>
       <c r="D81" s="59"/>
       <c r="E81" s="59" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="n">
         <v>45271</v>
       </c>
@@ -12168,13 +12285,13 @@
         <v>2</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>184</v>
+        <v>427</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12185,19 +12302,19 @@
         <v>3</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>397</v>
+        <v>428</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>398</v>
+        <v>429</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>399</v>
+        <v>430</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="n">
         <v>45271</v>
       </c>
@@ -12205,16 +12322,16 @@
         <v>4</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>401</v>
+        <v>433</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>186</v>
+        <v>435</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12225,17 +12342,17 @@
         <v>1</v>
       </c>
       <c r="C85" s="59" t="s">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="D85" s="59"/>
       <c r="E85" s="59" t="s">
-        <v>404</v>
+        <v>437</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="n">
         <v>45274</v>
       </c>
@@ -12243,16 +12360,16 @@
         <v>2</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="n">
         <v>45274</v>
       </c>
@@ -12260,16 +12377,16 @@
         <v>3</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>408</v>
+        <v>442</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="n">
         <v>45274</v>
       </c>
@@ -12277,16 +12394,16 @@
         <v>4</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>411</v>
+        <v>446</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="57" t="n">
         <v>45278</v>
       </c>
@@ -12294,17 +12411,17 @@
         <v>1</v>
       </c>
       <c r="C89" s="59" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="D89" s="59"/>
       <c r="E89" s="59" t="s">
-        <v>413</v>
+        <v>449</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="n">
         <v>45278</v>
       </c>
@@ -12312,16 +12429,16 @@
         <v>2</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>414</v>
+        <v>451</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="54" t="n">
         <v>45278</v>
       </c>
@@ -12329,20 +12446,20 @@
         <v>3</v>
       </c>
       <c r="C91" s="56" t="s">
-        <v>416</v>
+        <v>454</v>
       </c>
       <c r="D91" s="56"/>
       <c r="E91" s="56" t="s">
-        <v>417</v>
+        <v>455</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>195</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -12356,7 +12473,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C64"/>
-  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
@@ -13065,7 +13182,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -13079,7 +13196,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I64"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.19"/>
@@ -13098,22 +13215,22 @@
         <v>58</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>418</v>
+        <v>457</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>420</v>
+        <v>459</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>422</v>
+        <v>461</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>423</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13127,13 +13244,13 @@
         <v>215</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>424</v>
+        <v>463</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>425</v>
+        <v>464</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13147,10 +13264,10 @@
         <v>217</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>427</v>
+        <v>466</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>428</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13164,11 +13281,11 @@
         <v>219</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>429</v>
+        <v>468</v>
       </c>
       <c r="E4" s="56"/>
       <c r="F4" s="0" t="s">
-        <v>430</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13185,7 +13302,7 @@
         <v>64</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>431</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13236,7 +13353,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>432</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13250,10 +13367,10 @@
         <v>231</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>434</v>
+        <v>473</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>45032</v>
@@ -13270,13 +13387,13 @@
         <v>233</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>435</v>
+        <v>474</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>436</v>
+        <v>475</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>432</v>
+        <v>471</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>45032</v>
@@ -13296,13 +13413,13 @@
         <v>235</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>437</v>
+        <v>476</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>438</v>
+        <v>477</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>432</v>
+        <v>471</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>45031</v>
@@ -13356,10 +13473,10 @@
         <v>241</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>439</v>
+        <v>478</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>439</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13373,10 +13490,10 @@
         <v>242</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>440</v>
+        <v>479</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>441</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13390,10 +13507,10 @@
         <v>244</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>442</v>
+        <v>481</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>443</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13407,10 +13524,10 @@
         <v>246</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>444</v>
+        <v>483</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>445</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13424,10 +13541,10 @@
         <v>248</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>446</v>
+        <v>485</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>447</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13441,10 +13558,10 @@
         <v>250</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>448</v>
+        <v>487</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>449</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13458,10 +13575,10 @@
         <v>252</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>451</v>
+        <v>490</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13654,7 +13771,7 @@
       </c>
       <c r="C54" s="64"/>
       <c r="D54" s="0" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5" t="n">
@@ -13664,7 +13781,7 @@
         <v>45383</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>452</v>
+        <v>491</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13676,7 +13793,7 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="0" t="s">
-        <v>453</v>
+        <v>492</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5" t="n">
@@ -13686,7 +13803,7 @@
         <v>45383</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>452</v>
+        <v>491</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13698,7 +13815,7 @@
       </c>
       <c r="C56" s="64"/>
       <c r="D56" s="0" t="s">
-        <v>454</v>
+        <v>493</v>
       </c>
       <c r="G56" s="5" t="n">
         <v>45383</v>
@@ -13707,7 +13824,7 @@
         <v>45383</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>452</v>
+        <v>491</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13719,7 +13836,7 @@
       </c>
       <c r="C63" s="24"/>
       <c r="D63" s="0" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13731,13 +13848,13 @@
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="0" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -13751,7 +13868,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E58"/>
-  <sheetFormatPr defaultColWidth="11.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.39"/>
@@ -13767,10 +13884,10 @@
         <v>196</v>
       </c>
       <c r="C1" s="65" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>456</v>
+        <v>495</v>
       </c>
       <c r="E1" s="66" t="s">
         <v>197</v>
@@ -13778,642 +13895,642 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>0.000167347651247531</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>460</v>
+        <v>499</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>0.00183374075083306</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>461</v>
+        <v>500</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>0.000272504256866232</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>463</v>
+        <v>502</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>0.0292681461802767</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>464</v>
+        <v>503</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>0.0408544513448368</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>0.0157046582446898</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>466</v>
+        <v>505</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>0.0370030470217893</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>0.00030485139103684</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>469</v>
+        <v>508</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>1.5753190717376E-006</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>0.00551306886663384</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>470</v>
+        <v>509</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>0.0203493517653912</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="67" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B13" s="67" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>471</v>
+        <v>510</v>
       </c>
       <c r="D13" s="67" t="n">
         <v>0.0093569117500219</v>
       </c>
       <c r="E13" s="67" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>7.16834396218083E-012</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>472</v>
+        <v>511</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>0.00567551921407011</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>0.0324084567043176</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>474</v>
+        <v>513</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>0.0152606785752719</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>475</v>
+        <v>514</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>0.0108783273244698</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="67" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B19" s="67" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="67" t="s">
-        <v>477</v>
+        <v>516</v>
       </c>
       <c r="D19" s="67" t="n">
         <v>6.6312123780865E-012</v>
       </c>
       <c r="E19" s="67" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>478</v>
+        <v>517</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>7.80299610061578E-006</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>479</v>
+        <v>518</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>0.0179897142885999</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>480</v>
+        <v>519</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>0.00452884431580007</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>481</v>
+        <v>520</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>3.87812384813526E-006</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>1.15036720241586E-005</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>483</v>
+        <v>522</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>5.0802631434574E-007</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>461</v>
+        <v>500</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>3.48005489557259E-005</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="D27" s="0" t="n">
         <v>0.000909303064193552</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>484</v>
+        <v>523</v>
       </c>
       <c r="D28" s="0" t="n">
         <v>0.00137042128127269</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>481</v>
+        <v>520</v>
       </c>
       <c r="D29" s="0" t="n">
         <v>0.0402955062172857</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>485</v>
+        <v>524</v>
       </c>
       <c r="D30" s="0" t="n">
         <v>0.0110877305932871</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="D31" s="0" t="n">
         <v>0.0399456110435245</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>487</v>
+        <v>526</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>488</v>
+        <v>527</v>
       </c>
       <c r="D32" s="0" t="n">
         <v>0.00862296916201926</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="67" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
       <c r="B33" s="67" t="n">
         <v>3</v>
       </c>
       <c r="C33" s="67" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="D33" s="67" t="n">
         <v>0.0482858559404872</v>
       </c>
       <c r="E33" s="67" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="67" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="B34" s="67" t="n">
         <v>2</v>
       </c>
       <c r="C34" s="67" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="D34" s="67" t="n">
         <v>0.00239737276432677</v>
       </c>
       <c r="E34" s="67" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="D35" s="0" t="n">
         <v>0.0404251274716832</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>493</v>
+        <v>532</v>
       </c>
       <c r="D36" s="0" t="n">
         <v>0.0213915212994397</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="D37" s="0" t="n">
         <v>0.0181306288529609</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="D38" s="0" t="n">
         <v>0.000371456787101544</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="67" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B39" s="67" t="n">
         <v>4</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="D39" s="67" t="n">
         <v>0.0259924251683769</v>
@@ -14424,13 +14541,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>498</v>
+        <v>537</v>
       </c>
       <c r="D40" s="0" t="n">
         <v>0.021951365810948</v>
@@ -14441,13 +14558,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="D41" s="0" t="n">
         <v>5.52169283538707E-007</v>
@@ -14458,13 +14575,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="D42" s="0" t="n">
         <v>4.46843053651836E-006</v>
@@ -14475,13 +14592,13 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B43" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>500</v>
+        <v>539</v>
       </c>
       <c r="D43" s="0" t="n">
         <v>5.99143685263841E-005</v>
@@ -14492,13 +14609,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="D44" s="0" t="n">
         <v>0.00818486262907165</v>
@@ -14509,13 +14626,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="D45" s="0" t="n">
         <v>0.00534908622982942</v>
@@ -14526,13 +14643,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="D46" s="0" t="n">
         <v>0.0183427990773176</v>
@@ -14543,13 +14660,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="B47" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="D47" s="0" t="n">
         <v>0.0450375913084286</v>
@@ -14560,13 +14677,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="D48" s="0" t="n">
         <v>0.0137207438451637</v>
@@ -14577,13 +14694,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="D49" s="0" t="n">
         <v>0.0308159014622524</v>
@@ -14594,13 +14711,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>506</v>
+        <v>545</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="D50" s="0" t="n">
         <v>0.0139354605217081</v>
@@ -14611,13 +14728,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>506</v>
+        <v>545</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>507</v>
+        <v>546</v>
       </c>
       <c r="D51" s="0" t="n">
         <v>0.00408222428481898</v>
@@ -14628,13 +14745,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>506</v>
+        <v>545</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>508</v>
+        <v>547</v>
       </c>
       <c r="D52" s="0" t="n">
         <v>0.0352229638559858</v>
@@ -14645,13 +14762,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>475</v>
+        <v>514</v>
       </c>
       <c r="D53" s="0" t="n">
         <v>0.0113482599171506</v>
@@ -14662,13 +14779,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>510</v>
+        <v>549</v>
       </c>
       <c r="D54" s="0" t="n">
         <v>0.0312767076889777</v>
@@ -14679,13 +14796,13 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>511</v>
+        <v>550</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>512</v>
+        <v>551</v>
       </c>
       <c r="D55" s="0" t="n">
         <v>0.00517590455590829</v>
@@ -14696,13 +14813,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="D56" s="0" t="n">
         <v>0.00914148375940307</v>
@@ -14713,13 +14830,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>512</v>
+        <v>551</v>
       </c>
       <c r="D57" s="0" t="n">
         <v>0.0368202416860903</v>
@@ -14730,13 +14847,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="B58" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
       <c r="D58" s="0" t="n">
         <v>0.00658281460550913</v>
@@ -14748,7 +14865,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -14762,7 +14879,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:S36"/>
-  <sheetFormatPr defaultColWidth="11.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.11"/>
@@ -14788,22 +14905,22 @@
         <v>196</v>
       </c>
       <c r="C1" s="65" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>516</v>
+        <v>555</v>
       </c>
       <c r="E1" s="65" t="s">
-        <v>517</v>
+        <v>556</v>
       </c>
       <c r="F1" s="65" t="s">
-        <v>518</v>
+        <v>557</v>
       </c>
       <c r="G1" s="65" t="s">
-        <v>519</v>
+        <v>558</v>
       </c>
       <c r="H1" s="65" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
       <c r="I1" s="66" t="s">
         <v>197</v>
@@ -14819,19 +14936,19 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>521</v>
+        <v>560</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>523</v>
+        <v>562</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>0.787376130022259</v>
@@ -14840,27 +14957,27 @@
         <v>0.00141302462633323</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>524</v>
+        <v>563</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>525</v>
+        <v>564</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>527</v>
+        <v>566</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>0.714149977396184</v>
@@ -14869,27 +14986,27 @@
         <v>0.00412742172835764</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>528</v>
+        <v>567</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>0.72507271030454</v>
@@ -14898,27 +15015,27 @@
         <v>0.00358126617515756</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>530</v>
+        <v>569</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>531</v>
+        <v>570</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>0.734398082547392</v>
@@ -14927,27 +15044,27 @@
         <v>0.00315892887014564</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>532</v>
+        <v>571</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>533</v>
+        <v>572</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>534</v>
+        <v>573</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>0.737640600753071</v>
@@ -14956,27 +15073,27 @@
         <v>0.00302108700727468</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>535</v>
+        <v>574</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>534</v>
+        <v>573</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>0.715588361621035</v>
@@ -14985,27 +15102,27 @@
         <v>0.00405219461072609</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>536</v>
+        <v>575</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>470</v>
+        <v>509</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>527</v>
+        <v>566</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>0.784349723093875</v>
@@ -15014,27 +15131,27 @@
         <v>0.00148681503277446</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>537</v>
+        <v>576</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>538</v>
+        <v>577</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>523</v>
+        <v>562</v>
       </c>
       <c r="F9" s="0" t="n">
         <v>0.730766294167097</v>
@@ -15043,27 +15160,27 @@
         <v>0.00331876839660095</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>539</v>
+        <v>578</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>538</v>
+        <v>577</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>534</v>
+        <v>573</v>
       </c>
       <c r="F10" s="0" t="n">
         <v>0.846114075952503</v>
@@ -15072,27 +15189,27 @@
         <v>0.000443570824989244</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>540</v>
+        <v>579</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>541</v>
+        <v>580</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>523</v>
+        <v>562</v>
       </c>
       <c r="F11" s="0" t="n">
         <v>0.707474625239755</v>
@@ -15101,27 +15218,27 @@
         <v>0.00449016011444848</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>542</v>
+        <v>581</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>543</v>
+        <v>582</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>544</v>
+        <v>583</v>
       </c>
       <c r="F12" s="0" t="n">
         <v>0.785878208761381</v>
@@ -15130,27 +15247,27 @@
         <v>0.00144920361429895</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>545</v>
+        <v>584</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>479</v>
+        <v>518</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
       <c r="F13" s="0" t="n">
         <v>0.780344297275339</v>
@@ -15159,27 +15276,27 @@
         <v>0.00158876527841905</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>546</v>
+        <v>585</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>547</v>
+        <v>586</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>548</v>
+        <v>587</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>549</v>
+        <v>588</v>
       </c>
       <c r="F14" s="0" t="n">
         <v>0.707129353187573</v>
@@ -15188,27 +15305,27 @@
         <v>0.00450954256313961</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>550</v>
+        <v>589</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>548</v>
+        <v>587</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>551</v>
+        <v>590</v>
       </c>
       <c r="F15" s="0" t="n">
         <v>0.803988782853755</v>
@@ -15217,27 +15334,27 @@
         <v>0.00105462762655855</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>552</v>
+        <v>591</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>548</v>
+        <v>587</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>553</v>
+        <v>592</v>
       </c>
       <c r="F16" s="0" t="n">
         <v>0.763699249257595</v>
@@ -15246,27 +15363,27 @@
         <v>0.00206810438085801</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>554</v>
+        <v>593</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="67" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B17" s="67" t="n">
         <v>3</v>
       </c>
       <c r="C17" s="67" t="s">
-        <v>471</v>
+        <v>510</v>
       </c>
       <c r="D17" s="67" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E17" s="67" t="s">
-        <v>544</v>
+        <v>583</v>
       </c>
       <c r="F17" s="67" t="n">
         <v>0.881204837525589</v>
@@ -15275,27 +15392,27 @@
         <v>0.000176549182897429</v>
       </c>
       <c r="H17" s="67" t="s">
-        <v>555</v>
+        <v>594</v>
       </c>
       <c r="I17" s="67" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>556</v>
+        <v>595</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>548</v>
+        <v>587</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>549</v>
+        <v>588</v>
       </c>
       <c r="F18" s="0" t="n">
         <v>0.707101280411521</v>
@@ -15304,27 +15421,27 @@
         <v>0.00451112119911595</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>557</v>
+        <v>596</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>558</v>
+        <v>597</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>531</v>
+        <v>570</v>
       </c>
       <c r="F19" s="0" t="n">
         <v>0.751328262794826</v>
@@ -15333,27 +15450,27 @@
         <v>0.00248752021453756</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>559</v>
+        <v>598</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>523</v>
+        <v>562</v>
       </c>
       <c r="F20" s="0" t="n">
         <v>0.749550371405668</v>
@@ -15362,27 +15479,27 @@
         <v>0.00255256196778632</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>560</v>
+        <v>599</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="67" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B21" s="67" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="67" t="s">
-        <v>477</v>
+        <v>516</v>
       </c>
       <c r="D21" s="67" t="s">
-        <v>548</v>
+        <v>587</v>
       </c>
       <c r="E21" s="67" t="s">
-        <v>551</v>
+        <v>590</v>
       </c>
       <c r="F21" s="67" t="n">
         <v>0.720424149392981</v>
@@ -15391,27 +15508,27 @@
         <v>0.0038067080589425</v>
       </c>
       <c r="H21" s="67" t="s">
-        <v>561</v>
+        <v>600</v>
       </c>
       <c r="I21" s="67" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C22" s="0" t="s">
+        <v>601</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>561</v>
+      </c>
+      <c r="E22" s="0" t="s">
         <v>562</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>522</v>
-      </c>
-      <c r="E22" s="0" t="s">
-        <v>523</v>
       </c>
       <c r="F22" s="0" t="n">
         <v>0.707149139381861</v>
@@ -15420,27 +15537,27 @@
         <v>0.00450843015836554</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>563</v>
+        <v>602</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>562</v>
+        <v>601</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>534</v>
+        <v>573</v>
       </c>
       <c r="F23" s="0" t="n">
         <v>0.832865788003454</v>
@@ -15449,27 +15566,27 @@
         <v>0.000595776942024419</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>564</v>
+        <v>603</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>487</v>
+        <v>526</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>565</v>
+        <v>604</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>544</v>
+        <v>583</v>
       </c>
       <c r="F24" s="0" t="n">
         <v>0.74158029584605</v>
@@ -15478,27 +15595,27 @@
         <v>0.0028596364130994</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>566</v>
+        <v>605</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="67" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
       <c r="B25" s="67" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="67" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="D25" s="67" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="E25" s="67" t="s">
-        <v>567</v>
+        <v>606</v>
       </c>
       <c r="F25" s="67" t="n">
         <v>0.735073400638693</v>
@@ -15507,27 +15624,27 @@
         <v>0.00312984579624553</v>
       </c>
       <c r="H25" s="67" t="s">
-        <v>568</v>
+        <v>607</v>
       </c>
       <c r="I25" s="67" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="B26" s="67" t="n">
         <v>2</v>
       </c>
       <c r="C26" s="67" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="D26" s="67" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="E26" s="67" t="s">
-        <v>567</v>
+        <v>606</v>
       </c>
       <c r="F26" s="67" t="n">
         <v>0.711185571486803</v>
@@ -15536,27 +15653,27 @@
         <v>0.00428571572931137</v>
       </c>
       <c r="H26" s="67" t="s">
-        <v>569</v>
+        <v>608</v>
       </c>
       <c r="I26" s="67" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>570</v>
+        <v>609</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>510</v>
+        <v>549</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>527</v>
+        <v>566</v>
       </c>
       <c r="F27" s="0" t="n">
         <v>0.72106861365433</v>
@@ -15565,27 +15682,27 @@
         <v>0.00377484369911458</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>571</v>
+        <v>610</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="67" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B28" s="67" t="n">
         <v>4</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="D28" s="67" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="E28" s="67" t="s">
-        <v>527</v>
+        <v>566</v>
       </c>
       <c r="F28" s="67" t="n">
         <v>0.737807282466348</v>
@@ -15594,7 +15711,7 @@
         <v>0.0030141233437616</v>
       </c>
       <c r="H28" s="67" t="s">
-        <v>572</v>
+        <v>611</v>
       </c>
       <c r="I28" s="67" t="s">
         <v>205</v>
@@ -15602,19 +15719,19 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
       <c r="F29" s="0" t="n">
         <v>0.733031250915402</v>
@@ -15623,7 +15740,7 @@
         <v>0.00321840215280912</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>573</v>
+        <v>612</v>
       </c>
       <c r="I29" s="0" t="s">
         <v>205</v>
@@ -15631,19 +15748,19 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
       <c r="F30" s="0" t="n">
         <v>0.723125387871428</v>
@@ -15652,7 +15769,7 @@
         <v>0.00367446840750216</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>574</v>
+        <v>613</v>
       </c>
       <c r="I30" s="0" t="s">
         <v>205</v>
@@ -15660,19 +15777,19 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>575</v>
+        <v>614</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
       <c r="F31" s="0" t="n">
         <v>0.713139104979482</v>
@@ -15681,7 +15798,7 @@
         <v>0.0041809052804653</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>576</v>
+        <v>615</v>
       </c>
       <c r="I31" s="0" t="s">
         <v>205</v>
@@ -15689,19 +15806,19 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>577</v>
+        <v>616</v>
       </c>
       <c r="F32" s="0" t="n">
         <v>0.807758238850952</v>
@@ -15710,7 +15827,7 @@
         <v>0.000983606536464546</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>578</v>
+        <v>617</v>
       </c>
       <c r="I32" s="0" t="s">
         <v>205</v>
@@ -15718,19 +15835,19 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>579</v>
+        <v>618</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>472</v>
+        <v>511</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>531</v>
+        <v>570</v>
       </c>
       <c r="F33" s="0" t="n">
         <v>0.769683282494715</v>
@@ -15739,7 +15856,7 @@
         <v>0.0018850560139879</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>580</v>
+        <v>619</v>
       </c>
       <c r="I33" s="0" t="s">
         <v>205</v>
@@ -15747,19 +15864,19 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>579</v>
+        <v>618</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>548</v>
+        <v>587</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>551</v>
+        <v>590</v>
       </c>
       <c r="F34" s="0" t="n">
         <v>0.727748137795628</v>
@@ -15768,7 +15885,7 @@
         <v>0.00345607911942881</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>581</v>
+        <v>620</v>
       </c>
       <c r="I34" s="0" t="s">
         <v>205</v>
@@ -15776,19 +15893,19 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>582</v>
+        <v>621</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>548</v>
+        <v>587</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>549</v>
+        <v>588</v>
       </c>
       <c r="F35" s="0" t="n">
         <v>0.741751688201506</v>
@@ -15797,7 +15914,7 @@
         <v>0.00285276032610502</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>583</v>
+        <v>622</v>
       </c>
       <c r="I35" s="0" t="s">
         <v>205</v>
@@ -15805,19 +15922,19 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>475</v>
+        <v>514</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>567</v>
+        <v>606</v>
       </c>
       <c r="F36" s="0" t="n">
         <v>0.807996431921935</v>
@@ -15826,7 +15943,7 @@
         <v>0.000979239335847504</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>584</v>
+        <v>623</v>
       </c>
       <c r="I36" s="0" t="s">
         <v>205</v>
@@ -15835,7 +15952,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>

--- a/recording_metadata/Cortana_Recording_Metadata.xlsx
+++ b/recording_metadata/Cortana_Recording_Metadata.xlsx
@@ -12472,7 +12472,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13176,6 +13176,72 @@
         <v>3</v>
       </c>
       <c r="C64" s="0" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="n">
+        <v>45198</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="n">
+        <v>45226</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5" t="n">
+        <v>45226</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="5" t="n">
+        <v>45242</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5" t="n">
+        <v>45267</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="5" t="n">
+        <v>45274</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" s="0" t="s">
         <v>205</v>
       </c>
     </row>
